--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -5,9 +5,7 @@
   <sheets>
     <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$I$148</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
@@ -15,15 +13,51 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={6a8c95c9-41a0-4d28-85c3-48c0f00bd724}</author>
-    <author>tc={847b52c0-c204-4770-9138-8be7fc944349}</author>
-    <author>tc={85fc0caf-8dbc-4c92-9b62-7d568692d394}</author>
-    <author>tc={87910e70-5c5b-42b9-8725-e4b749767f96}</author>
-    <author>tc={94624eef-1097-4ded-86a5-bbec28381ebf}</author>
-    <author>tc={980935ad-ee7e-4c23-b24e-dcc56b1fa937}</author>
+    <author>tc={5d68f90f-38ce-4629-84cf-5ce13831de2e}</author>
+    <author>tc={6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}</author>
+    <author>tc={6c819519-80f7-40a6-8993-dec6f5e202f3}</author>
+    <author>tc={6f9b6446-98ce-4746-877b-23e4873605b9}</author>
+    <author>tc={7012e398-b5ba-4ce9-9813-baf3af072841}</author>
+    <author>tc={c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{6a8c95c9-41a0-4d28-85c3-48c0f00bd724}" ref="H41">
+    <comment authorId="0" xr:uid="{5d68f90f-38ce-4629-84cf-5ce13831de2e}" ref="G133">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Le cambiaron la transversalidad
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}" ref="F89">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actalmente es un Lineamiento de Operación
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{6c819519-80f7-40a6-8993-dec6f5e202f3}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con una clasificación programática con letra E
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{6f9b6446-98ce-4746-877b-23e4873605b9}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con clasificación Programpatica  E
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{7012e398-b5ba-4ce9-9813-baf3af072841}" ref="H41">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,25 +66,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{847b52c0-c204-4770-9138-8be7fc944349}" ref="G133">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Le cambiaron la transversalidad
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{85fc0caf-8dbc-4c92-9b62-7d568692d394}" ref="F89">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actalmente es un Lineamiento de Operación
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{87910e70-5c5b-42b9-8725-e4b749767f96}" ref="A1">
+    <comment authorId="5" xr:uid="{c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,30 +75,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{94624eef-1097-4ded-86a5-bbec28381ebf}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con una clasificación programática con letra E
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{980935ad-ee7e-4c23-b24e-dcc56b1fa937}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="373">
   <si>
     <t>UP</t>
   </si>
@@ -109,6 +107,9 @@
   </si>
   <si>
     <t>Estatal / Federal</t>
+  </si>
+  <si>
+    <t>Clave ROP</t>
   </si>
   <si>
     <t>02</t>
@@ -1267,7 +1268,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1291,9 +1292,6 @@
     </xf>
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1319,9 +1317,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{44d6f299-cc4e-4a59-853b-2ca5a3bc520a}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{70e60634-4afb-4d5e-9a07-77ec8f49620e}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{2e756a8f-68b6-48af-88e0-fabb66555cb2}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{5d1e9f7a-8c5f-4440-ad90-765d2213032c}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1521,22 +1519,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{70e60634-4afb-4d5e-9a07-77ec8f49620e}" id="{6a8c95c9-41a0-4d28-85c3-48c0f00bd724}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" id="{7012e398-b5ba-4ce9-9813-baf3af072841}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{44d6f299-cc4e-4a59-853b-2ca5a3bc520a}" id="{85fc0caf-8dbc-4c92-9b62-7d568692d394}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{70e60634-4afb-4d5e-9a07-77ec8f49620e}" id="{87910e70-5c5b-42b9-8725-e4b749767f96}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" id="{c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{2e756a8f-68b6-48af-88e0-fabb66555cb2}" id="{847b52c0-c204-4770-9138-8be7fc944349}" done="0">
+  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{5d1e9f7a-8c5f-4440-ad90-765d2213032c}" id="{5d68f90f-38ce-4629-84cf-5ce13831de2e}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{44d6f299-cc4e-4a59-853b-2ca5a3bc520a}" id="{980935ad-ee7e-4c23-b24e-dcc56b1fa937}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6f9b6446-98ce-4746-877b-23e4873605b9}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{44d6f299-cc4e-4a59-853b-2ca5a3bc520a}" id="{94624eef-1097-4ded-86a5-bbec28381ebf}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6c819519-80f7-40a6-8993-dec6f5e202f3}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1556,7 +1554,7 @@
     <col customWidth="1" min="5" max="5" width="23.0"/>
     <col customWidth="1" min="6" max="6" width="6.5"/>
     <col customWidth="1" min="7" max="7" width="13.5"/>
-    <col customWidth="1" min="8" max="8" width="36.75"/>
+    <col customWidth="1" min="8" max="8" width="42.25"/>
     <col customWidth="1" min="9" max="9" width="15.0"/>
   </cols>
   <sheetData>
@@ -1588,7 +1586,9 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1608,33 +1608,36 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <v>001</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -1654,33 +1657,36 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <v>001</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -1700,33 +1706,36 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <v>001</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -1746,33 +1755,36 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J5" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <v>002</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1792,33 +1804,36 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <v>003</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1838,33 +1853,36 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J7" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <v>001</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1884,33 +1902,36 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J8" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <v>004</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1930,33 +1951,36 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J9" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <v>005</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1976,33 +2000,36 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <v>006</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -2022,33 +2049,36 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J11" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <v>007</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -2068,33 +2098,36 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J12" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <v>008</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -2114,33 +2147,36 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J13" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <v>009</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -2160,33 +2196,36 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J14" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <v>010</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -2206,33 +2245,36 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J15" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <v>011</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2252,33 +2294,36 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J16" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <v>012</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2298,33 +2343,36 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J17" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <v>013</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2344,33 +2392,36 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J18" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <v>014</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2390,33 +2441,36 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="F19" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J19" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <v>015</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2436,33 +2490,36 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="F20" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J20" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <v>016</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2482,33 +2539,36 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="F21" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J21" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <v>017</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2528,33 +2588,36 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J22" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <v>018</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2574,33 +2637,36 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <v>019</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2620,33 +2686,36 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="F24" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J24" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <v>020</v>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2666,33 +2735,36 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="F25" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J25" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <v>021</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2712,33 +2784,36 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J26" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <v>022</v>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2758,33 +2833,36 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F27" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J27" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <v>023</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2804,33 +2882,36 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F28" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J28" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <v>024</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2850,33 +2931,36 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F29" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J29" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <v>025</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2896,33 +2980,36 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F30" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J30" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <v>026</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2942,33 +3029,36 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <v>027</v>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2988,33 +3078,36 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D32" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J32" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <v>028</v>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -3034,33 +3127,36 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F33" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J33" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <v>029</v>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -3080,33 +3176,36 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D34" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F34" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <v>030</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -3126,33 +3225,36 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F35" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J35" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <v>031</v>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
@@ -3172,33 +3274,36 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F36" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="I36" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J36" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <v>031</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
@@ -3218,33 +3323,36 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="F37" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J37" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <v>032</v>
+      </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -3264,33 +3372,36 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J38" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <v>033</v>
+      </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -3310,33 +3421,36 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="I39" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="J39" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="J39" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <v>033</v>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -3356,33 +3470,36 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J40" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <v>034</v>
+      </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -3402,33 +3519,36 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J41" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <v>035</v>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -3448,33 +3568,36 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J42" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <v>036</v>
+      </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -3494,33 +3617,36 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J43" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <v>037</v>
+      </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -3540,33 +3666,36 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="I44" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="J44" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <v>037</v>
+      </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -3586,33 +3715,36 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J45" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <v>037</v>
+      </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -3632,33 +3764,36 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J46" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <v>038</v>
+      </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -3678,33 +3813,36 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F47" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J47" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <v>039</v>
+      </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -3724,33 +3862,36 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F48" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J48" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <v>040</v>
+      </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -3770,33 +3911,36 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F49" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J49" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <v>041</v>
+      </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -3816,33 +3960,36 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F50" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J50" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <v>042</v>
+      </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -3862,33 +4009,36 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F51" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J51" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <v>043</v>
+      </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -3908,33 +4058,36 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F52" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J52" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <v>044</v>
+      </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -3954,33 +4107,36 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F53" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J53" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <v>045</v>
+      </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -4000,33 +4156,36 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F54" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J54" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <v>046</v>
+      </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -4046,33 +4205,36 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D55" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F55" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J55" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <v>047</v>
+      </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -4092,33 +4254,36 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F56" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J56" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <v>048</v>
+      </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -4138,33 +4303,36 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F57" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J57" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <v>049</v>
+      </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -4184,33 +4352,36 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F58" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J58" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <v>050</v>
+      </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -4230,33 +4401,36 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F59" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J59" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <v>051</v>
+      </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4276,33 +4450,36 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D60" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F60" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J60" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <v>052</v>
+      </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -4322,33 +4499,36 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D61" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F61" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J61" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <v>053</v>
+      </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -4368,33 +4548,36 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D62" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F62" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J62" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <v>054</v>
+      </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -4414,33 +4597,36 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D63" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F63" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J63" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J63" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <v>055</v>
+      </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -4460,33 +4646,36 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D64" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F64" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J64" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <v>056</v>
+      </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -4506,33 +4695,36 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D65" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F65" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J65" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <v>057</v>
+      </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -4552,33 +4744,36 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D66" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F66" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J66" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <v>058</v>
+      </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4598,33 +4793,36 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D67" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F67" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J67" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <v>059</v>
+      </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -4644,33 +4842,36 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D68" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="F68" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J68" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <v>060</v>
+      </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -4690,33 +4891,36 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="F69" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J69" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <v>061</v>
+      </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -4736,33 +4940,36 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D70" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="F70" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J70" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <v>062</v>
+      </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -4782,33 +4989,36 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D71" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="F71" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J71" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <v>063</v>
+      </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -4828,33 +5038,36 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J72" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
+      </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -4874,33 +5087,36 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G73" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H73" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="I73" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J73" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
+      </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -4920,33 +5136,36 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J74" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
+      </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -4966,33 +5185,36 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J75" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
+      </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -5012,33 +5234,36 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J76" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <v>064</v>
+      </c>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -5058,33 +5283,36 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J77" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <v>065</v>
+      </c>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
@@ -5104,33 +5332,36 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J78" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J78" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <v>066</v>
+      </c>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -5150,33 +5381,36 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J79" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <v>067</v>
+      </c>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -5196,33 +5430,36 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J80" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <v>068</v>
+      </c>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -5242,33 +5479,36 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J81" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J81" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <v>069</v>
+      </c>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -5288,33 +5528,36 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G82" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I82" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="H82" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J82" s="4"/>
+      <c r="J82" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <v>070</v>
+      </c>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -5334,33 +5577,36 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J83" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <v>071</v>
+      </c>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -5380,33 +5626,36 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J84" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <v>072</v>
+      </c>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -5426,33 +5675,36 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J85" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <v>073</v>
+      </c>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
@@ -5472,33 +5724,36 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J86" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <v>074</v>
+      </c>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
@@ -5518,33 +5773,36 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J87" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <v>075</v>
+      </c>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
@@ -5564,33 +5822,36 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G88" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H88" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="H88" s="5" t="s">
-        <v>232</v>
-      </c>
       <c r="I88" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J88" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <v>075</v>
+      </c>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
@@ -5610,33 +5871,36 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>235</v>
-      </c>
       <c r="F89" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J89" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J89" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <v>076</v>
+      </c>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -5656,33 +5920,36 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J90" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <v>077</v>
+      </c>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5702,33 +5969,36 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G91" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="H91" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="H91" s="5" t="s">
-        <v>245</v>
-      </c>
       <c r="I91" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J91" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J91" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <v>077</v>
+      </c>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -5748,33 +6018,36 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D92" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>250</v>
+        <v>14</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J92" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <v>078</v>
+      </c>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -5794,33 +6067,36 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>252</v>
+        <v>14</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J93" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <v>079</v>
+      </c>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -5840,33 +6116,36 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D94" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F94" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J94" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <v>080</v>
+      </c>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -5886,33 +6165,36 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D95" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F95" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J95" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <v>081</v>
+      </c>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -5932,33 +6214,36 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F96" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J96" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <v>082</v>
+      </c>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -5978,33 +6263,36 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="F97" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J97" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <v>083</v>
+      </c>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -6024,33 +6312,36 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J98" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J98" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <v>084</v>
+      </c>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -6070,33 +6361,36 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J99" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J99" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <v>085</v>
+      </c>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -6116,33 +6410,36 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J100" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J100" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <v>086</v>
+      </c>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -6162,33 +6459,36 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J101" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J101" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <v>087</v>
+      </c>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -6208,33 +6508,36 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J102" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J102" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <v>088</v>
+      </c>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -6254,33 +6557,36 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J103" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J103" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <v>089</v>
+      </c>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
@@ -6300,33 +6606,36 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J104" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J104" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <v>090</v>
+      </c>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
@@ -6346,33 +6655,36 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J105" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J105" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <v>091</v>
+      </c>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
@@ -6392,33 +6704,36 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J106" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J106" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <v>092</v>
+      </c>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
@@ -6438,33 +6753,36 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J107" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J107" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <v>093</v>
+      </c>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
@@ -6484,33 +6802,36 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J108" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J108" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <v>094</v>
+      </c>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
@@ -6530,33 +6851,36 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J109" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J109" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <v>095</v>
+      </c>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
@@ -6576,33 +6900,36 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J110" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J110" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <v>096</v>
+      </c>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
@@ -6622,33 +6949,36 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J111" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J111" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <v>097</v>
+      </c>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
@@ -6668,33 +6998,36 @@
     </row>
     <row r="112" ht="60.0" customHeight="1">
       <c r="A112" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J112" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J112" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <v>098</v>
+      </c>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
@@ -6714,33 +7047,36 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J113" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J113" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <v>099</v>
+      </c>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
@@ -6760,33 +7096,36 @@
     </row>
     <row r="114" ht="46.5" customHeight="1">
       <c r="A114" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J114" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J114" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <v>100</v>
+      </c>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
@@ -6806,33 +7145,36 @@
     </row>
     <row r="115" ht="46.5" customHeight="1">
       <c r="A115" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J115" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J115" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <v>101</v>
+      </c>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
@@ -6852,33 +7194,36 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J116" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J116" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <v>102</v>
+      </c>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
@@ -6898,33 +7243,36 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J117" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J117" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <v>103</v>
+      </c>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
@@ -6944,33 +7292,36 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J118" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J118" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <v>104</v>
+      </c>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
@@ -6990,33 +7341,36 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J119" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J119" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"105")</f>
+        <v>105</v>
+      </c>
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
@@ -7036,33 +7390,36 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="J120" s="4"/>
+        <v>218</v>
+      </c>
+      <c r="J120" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"106")</f>
+        <v>106</v>
+      </c>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
@@ -7082,33 +7439,36 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J121" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J121" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"107")</f>
+        <v>107</v>
+      </c>
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
@@ -7128,33 +7488,36 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J122" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J122" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"108")</f>
+        <v>108</v>
+      </c>
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
@@ -7174,33 +7537,36 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D123" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E123" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E123" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="F123" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J123" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J123" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"109")</f>
+        <v>109</v>
+      </c>
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
@@ -7220,33 +7586,36 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D124" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E124" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E124" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="F124" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J124" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J124" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"110")</f>
+        <v>110</v>
+      </c>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
@@ -7266,33 +7635,36 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D125" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E125" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E125" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="F125" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J125" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J125" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"111")</f>
+        <v>111</v>
+      </c>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
@@ -7312,33 +7684,36 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="F126" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J126" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="J126" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"112")</f>
+        <v>112</v>
+      </c>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
@@ -7358,33 +7733,36 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E127" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E127" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F127" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J127" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J127" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"113")</f>
+        <v>113</v>
+      </c>
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
@@ -7404,33 +7782,36 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D128" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E128" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E128" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F128" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J128" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J128" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"114")</f>
+        <v>114</v>
+      </c>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -7450,33 +7831,36 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D129" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E129" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E129" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F129" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J129" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J129" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"115")</f>
+        <v>115</v>
+      </c>
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -7496,33 +7880,36 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D130" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F130" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J130" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J130" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"116")</f>
+        <v>116</v>
+      </c>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
@@ -7542,33 +7929,36 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E131" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E131" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F131" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J131" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J131" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <v>117</v>
+      </c>
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
@@ -7588,33 +7978,36 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E132" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E132" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F132" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J132" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J132" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <v>118</v>
+      </c>
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
@@ -7634,33 +8027,36 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D133" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E133" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F133" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J133" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J133" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
+      </c>
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
@@ -7680,33 +8076,36 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D134" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E134" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E134" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F134" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J134" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J134" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <v>120</v>
+      </c>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
@@ -7726,33 +8125,36 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="E135" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E135" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="F135" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J135" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J135" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"121")</f>
+        <v>121</v>
+      </c>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
@@ -7772,33 +8174,36 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J136" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J136" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
+        <v>122</v>
+      </c>
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
@@ -7818,33 +8223,36 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G137" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="H137" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="H137" s="5" t="s">
-        <v>355</v>
-      </c>
       <c r="I137" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J137" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J137" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
+        <v>122</v>
+      </c>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
@@ -7864,33 +8272,36 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J138" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J138" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"123")</f>
+        <v>123</v>
+      </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
@@ -7910,33 +8321,36 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J139" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J139" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
+        <v>124</v>
+      </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
@@ -7956,33 +8370,36 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G140" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="H140" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H140" s="5" t="s">
-        <v>360</v>
-      </c>
       <c r="I140" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J140" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J140" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
+        <v>124</v>
+      </c>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
@@ -8002,33 +8419,36 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J141" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J141" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
+      </c>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
@@ -8048,33 +8468,36 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G142" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="H142" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="H142" s="5" t="s">
-        <v>363</v>
-      </c>
       <c r="I142" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J142" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J142" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
+      </c>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
@@ -8094,33 +8517,36 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J143" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J143" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
+      </c>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
@@ -8140,33 +8566,36 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J144" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J144" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
+      </c>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
@@ -8186,33 +8615,36 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J145" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J145" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"127")</f>
+        <v>127</v>
+      </c>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
@@ -8232,33 +8664,36 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J146" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J146" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
+      </c>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
@@ -8278,33 +8713,36 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="J147" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="J147" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
+      </c>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
@@ -8330,7 +8768,7 @@
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
-      <c r="H148" s="5"/>
+      <c r="H148" s="6"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
@@ -8414,7 +8852,6 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -8442,6 +8879,7 @@
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
+      <c r="H152" s="6"/>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
@@ -9190,14 +9628,14 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -9218,14 +9656,14 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="10"/>
-      <c r="B180" s="10"/>
-      <c r="C180" s="10"/>
-      <c r="D180" s="10"/>
-      <c r="E180" s="10"/>
-      <c r="F180" s="10"/>
-      <c r="G180" s="10"/>
-      <c r="H180" s="10"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -9246,14 +9684,14 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="10"/>
-      <c r="B181" s="10"/>
-      <c r="C181" s="10"/>
-      <c r="D181" s="10"/>
-      <c r="E181" s="10"/>
-      <c r="F181" s="10"/>
-      <c r="G181" s="10"/>
-      <c r="H181" s="10"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -9274,14 +9712,14 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="10"/>
-      <c r="B182" s="10"/>
-      <c r="C182" s="10"/>
-      <c r="D182" s="10"/>
-      <c r="E182" s="10"/>
-      <c r="F182" s="10"/>
-      <c r="G182" s="10"/>
-      <c r="H182" s="10"/>
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -9302,14 +9740,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="10"/>
-      <c r="B183" s="10"/>
-      <c r="C183" s="10"/>
-      <c r="D183" s="10"/>
-      <c r="E183" s="10"/>
-      <c r="F183" s="10"/>
-      <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -9330,14 +9768,14 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="10"/>
-      <c r="B184" s="10"/>
-      <c r="C184" s="10"/>
-      <c r="D184" s="10"/>
-      <c r="E184" s="10"/>
-      <c r="F184" s="10"/>
-      <c r="G184" s="10"/>
-      <c r="H184" s="10"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
+      <c r="F184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -9358,14 +9796,14 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="10"/>
-      <c r="B185" s="10"/>
-      <c r="C185" s="10"/>
-      <c r="D185" s="10"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="10"/>
-      <c r="G185" s="10"/>
-      <c r="H185" s="10"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -9386,14 +9824,14 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="10"/>
-      <c r="B186" s="10"/>
-      <c r="C186" s="10"/>
-      <c r="D186" s="10"/>
-      <c r="E186" s="10"/>
-      <c r="F186" s="10"/>
-      <c r="G186" s="10"/>
-      <c r="H186" s="10"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -9414,14 +9852,14 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="10"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="10"/>
-      <c r="D187" s="10"/>
-      <c r="E187" s="10"/>
-      <c r="F187" s="10"/>
-      <c r="G187" s="10"/>
-      <c r="H187" s="10"/>
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -9442,14 +9880,14 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
-      <c r="G188" s="10"/>
-      <c r="H188" s="10"/>
+      <c r="A188" s="9"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -9470,14 +9908,14 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
-      <c r="G189" s="10"/>
-      <c r="H189" s="10"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -9498,14 +9936,14 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
-      <c r="G190" s="10"/>
-      <c r="H190" s="10"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -9526,14 +9964,14 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10"/>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
-      <c r="G191" s="10"/>
-      <c r="H191" s="10"/>
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -34333,40 +34771,7 @@
       <c r="Y1076" s="4"/>
       <c r="Z1076" s="4"/>
     </row>
-    <row r="1077">
-      <c r="A1077" s="4"/>
-      <c r="B1077" s="4"/>
-      <c r="C1077" s="4"/>
-      <c r="D1077" s="4"/>
-      <c r="E1077" s="4"/>
-      <c r="F1077" s="4"/>
-      <c r="G1077" s="4"/>
-      <c r="H1077" s="4"/>
-      <c r="I1077" s="4"/>
-      <c r="J1077" s="4"/>
-      <c r="K1077" s="4"/>
-      <c r="L1077" s="4"/>
-      <c r="M1077" s="4"/>
-      <c r="N1077" s="4"/>
-      <c r="O1077" s="4"/>
-      <c r="P1077" s="4"/>
-      <c r="Q1077" s="4"/>
-      <c r="R1077" s="4"/>
-      <c r="S1077" s="4"/>
-      <c r="T1077" s="4"/>
-      <c r="U1077" s="4"/>
-      <c r="V1077" s="4"/>
-      <c r="W1077" s="4"/>
-      <c r="X1077" s="4"/>
-      <c r="Y1077" s="4"/>
-      <c r="Z1077" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$I$148">
-    <sortState ref="A1:I148">
-      <sortCondition ref="A1:A148"/>
-    </sortState>
-  </autoFilter>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
 </worksheet>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,15 +13,33 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={5d68f90f-38ce-4629-84cf-5ce13831de2e}</author>
-    <author>tc={6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}</author>
-    <author>tc={6c819519-80f7-40a6-8993-dec6f5e202f3}</author>
-    <author>tc={6f9b6446-98ce-4746-877b-23e4873605b9}</author>
-    <author>tc={7012e398-b5ba-4ce9-9813-baf3af072841}</author>
-    <author>tc={c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}</author>
+    <author>tc={9276e02c-6725-4ce9-b690-beadc8ee11fe}</author>
+    <author>tc={9423c150-3d8c-4943-9819-c3642c7fca26}</author>
+    <author>tc={99d95040-9722-4c41-953d-31e9db519275}</author>
+    <author>tc={a0b65cad-3480-49f7-ab26-5254011e6189}</author>
+    <author>tc={c5cc14ea-39e3-4a55-aee1-5e20d74894ae}</author>
+    <author>tc={f2c81bc6-0cdd-4a7e-a747-c8e34427047d}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{5d68f90f-38ce-4629-84cf-5ce13831de2e}" ref="G133">
+    <comment authorId="0" xr:uid="{9276e02c-6725-4ce9-b690-beadc8ee11fe}" ref="H41">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{9423c150-3d8c-4943-9819-c3642c7fca26}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{99d95040-9722-4c41-953d-31e9db519275}" ref="G133">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +48,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}" ref="F89">
+    <comment authorId="3" xr:uid="{a0b65cad-3480-49f7-ab26-5254011e6189}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con clasificación Programpatica  E
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{c5cc14ea-39e3-4a55-aee1-5e20d74894ae}" ref="F89">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,39 +66,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{6c819519-80f7-40a6-8993-dec6f5e202f3}" ref="F18">
+    <comment authorId="5" xr:uid="{f2c81bc6-0cdd-4a7e-a747-c8e34427047d}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	Actualmente cuenta con una clasificación programática con letra E
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{6f9b6446-98ce-4746-877b-23e4873605b9}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{7012e398-b5ba-4ce9-9813-baf3af072841}" ref="H41">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
 </t>
       </text>
     </comment>
@@ -109,7 +109,7 @@
     <t>Estatal / Federal</t>
   </si>
   <si>
-    <t>Clave ROP</t>
+    <t>Clave ROP_LOP</t>
   </si>
   <si>
     <t>02</t>
@@ -1317,9 +1317,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{5d1e9f7a-8c5f-4440-ad90-765d2213032c}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{bd75250c-cd9b-4fe1-bd3b-b89d0309750d}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1519,22 +1519,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" id="{7012e398-b5ba-4ce9-9813-baf3af072841}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" id="{9276e02c-6725-4ce9-b690-beadc8ee11fe}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6b4661c6-0dc8-4d2b-bdc3-16f0039c04f0}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{c5cc14ea-39e3-4a55-aee1-5e20d74894ae}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{b2e042d1-fa99-4787-a2b9-0a227723c2ce}" id="{c4d68e17-7d1f-4a4f-b774-5c2b39c421cf}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" id="{9423c150-3d8c-4943-9819-c3642c7fca26}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{5d1e9f7a-8c5f-4440-ad90-765d2213032c}" id="{5d68f90f-38ce-4629-84cf-5ce13831de2e}" done="0">
+  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{bd75250c-cd9b-4fe1-bd3b-b89d0309750d}" id="{99d95040-9722-4c41-953d-31e9db519275}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6f9b6446-98ce-4746-877b-23e4873605b9}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{a0b65cad-3480-49f7-ab26-5254011e6189}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{c21d4575-cc01-41e9-b9e8-94421cf37a64}" id="{6c819519-80f7-40a6-8993-dec6f5e202f3}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{f2c81bc6-0cdd-4a7e-a747-c8e34427047d}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,15 +13,60 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={9276e02c-6725-4ce9-b690-beadc8ee11fe}</author>
-    <author>tc={9423c150-3d8c-4943-9819-c3642c7fca26}</author>
-    <author>tc={99d95040-9722-4c41-953d-31e9db519275}</author>
-    <author>tc={a0b65cad-3480-49f7-ab26-5254011e6189}</author>
-    <author>tc={c5cc14ea-39e3-4a55-aee1-5e20d74894ae}</author>
-    <author>tc={f2c81bc6-0cdd-4a7e-a747-c8e34427047d}</author>
+    <author>tc={67b169c8-f19c-46f1-b85b-7ec54da15671}</author>
+    <author>tc={7ae6649a-807e-4015-b38f-37eaa2c6b1fd}</author>
+    <author>tc={c113079d-b908-448c-8b48-45a8dab1b0a2}</author>
+    <author>tc={d8aac47c-72e6-4f10-8ef6-685c6c147d6d}</author>
+    <author>tc={e1469053-c5ab-4df9-9e14-d910d17d7cd4}</author>
+    <author>tc={f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{9276e02c-6725-4ce9-b690-beadc8ee11fe}" ref="H41">
+    <comment authorId="0" xr:uid="{67b169c8-f19c-46f1-b85b-7ec54da15671}" ref="G136">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Le cambiaron la transversalidad
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{7ae6649a-807e-4015-b38f-37eaa2c6b1fd}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{c113079d-b908-448c-8b48-45a8dab1b0a2}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con clasificación Programpatica  E
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{d8aac47c-72e6-4f10-8ef6-685c6c147d6d}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con una clasificación programática con letra E
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{e1469053-c5ab-4df9-9e14-d910d17d7cd4}" ref="F89">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actalmente es un Lineamiento de Operación
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}" ref="H41">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,57 +75,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{9423c150-3d8c-4943-9819-c3642c7fca26}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{99d95040-9722-4c41-953d-31e9db519275}" ref="G133">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Le cambiaron la transversalidad
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{a0b65cad-3480-49f7-ab26-5254011e6189}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{c5cc14ea-39e3-4a55-aee1-5e20d74894ae}" ref="F89">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actalmente es un Lineamiento de Operación
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{f2c81bc6-0cdd-4a7e-a747-c8e34427047d}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con una clasificación programática con letra E
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="379">
   <si>
     <t>UP</t>
   </si>
@@ -1075,6 +1075,27 @@
   </si>
   <si>
     <t>Mejoramiento de Vivienda</t>
+  </si>
+  <si>
+    <t>S5V_C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viviendas para contribuir a la reducción del déficit habitacional cuantitativo construidas
+</t>
+  </si>
+  <si>
+    <t>S5V_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obras de infraestructura para brindar servicios básicos ejecutadas
+</t>
+  </si>
+  <si>
+    <t>S5V_D6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obras de urbanización con el propósito de generar suelo urbano asequible ejecutadas
+</t>
   </si>
   <si>
     <t>S5V_D2</t>
@@ -1317,9 +1338,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{bd75250c-cd9b-4fe1-bd3b-b89d0309750d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{1df09a3f-a647-4871-9c3b-258f0246c161}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{a10f06c8-0ecf-4222-9d57-eabe78a1b637}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1519,22 +1540,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" id="{9276e02c-6725-4ce9-b690-beadc8ee11fe}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" id="{f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{c5cc14ea-39e3-4a55-aee1-5e20d74894ae}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{e1469053-c5ab-4df9-9e14-d910d17d7cd4}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{30e8fe6a-d8d7-4571-9951-3fe24ed3e0b3}" id="{9423c150-3d8c-4943-9819-c3642c7fca26}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" id="{7ae6649a-807e-4015-b38f-37eaa2c6b1fd}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{bd75250c-cd9b-4fe1-bd3b-b89d0309750d}" id="{99d95040-9722-4c41-953d-31e9db519275}" done="0">
+  <x18tc:threadedComment ref="G136" dT="2026-08-03T23:05:51.00" personId="{a10f06c8-0ecf-4222-9d57-eabe78a1b637}" id="{67b169c8-f19c-46f1-b85b-7ec54da15671}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{a0b65cad-3480-49f7-ab26-5254011e6189}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{c113079d-b908-448c-8b48-45a8dab1b0a2}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{55a38f73-f4ea-478b-8f90-c08aaec3dcb6}" id="{f2c81bc6-0cdd-4a7e-a747-c8e34427047d}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{d8aac47c-72e6-4f10-8ef6-685c6c147d6d}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1635,7 +1656,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K2" s="4"/>
@@ -1684,7 +1705,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K3" s="4"/>
@@ -1733,7 +1754,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K4" s="4"/>
@@ -1782,7 +1803,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"002")</f>
         <v>002</v>
       </c>
       <c r="K5" s="4"/>
@@ -1831,7 +1852,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"003")</f>
         <v>003</v>
       </c>
       <c r="K6" s="4"/>
@@ -1880,7 +1901,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K7" s="4"/>
@@ -1929,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"004")</f>
         <v>004</v>
       </c>
       <c r="K8" s="4"/>
@@ -1978,7 +1999,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"005")</f>
         <v>005</v>
       </c>
       <c r="K9" s="4"/>
@@ -2027,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"006")</f>
         <v>006</v>
       </c>
       <c r="K10" s="4"/>
@@ -2076,7 +2097,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"007")</f>
         <v>007</v>
       </c>
       <c r="K11" s="4"/>
@@ -2125,7 +2146,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"008")</f>
         <v>008</v>
       </c>
       <c r="K12" s="4"/>
@@ -2174,7 +2195,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"009")</f>
         <v>009</v>
       </c>
       <c r="K13" s="4"/>
@@ -2223,7 +2244,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"010")</f>
         <v>010</v>
       </c>
       <c r="K14" s="4"/>
@@ -2272,7 +2293,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"011")</f>
         <v>011</v>
       </c>
       <c r="K15" s="4"/>
@@ -2321,7 +2342,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"012")</f>
         <v>012</v>
       </c>
       <c r="K16" s="4"/>
@@ -2370,7 +2391,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"013")</f>
         <v>013</v>
       </c>
       <c r="K17" s="4"/>
@@ -2419,7 +2440,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"014")</f>
         <v>014</v>
       </c>
       <c r="K18" s="4"/>
@@ -2468,7 +2489,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"015")</f>
         <v>015</v>
       </c>
       <c r="K19" s="4"/>
@@ -2517,7 +2538,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"016")</f>
         <v>016</v>
       </c>
       <c r="K20" s="4"/>
@@ -2566,7 +2587,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"017")</f>
         <v>017</v>
       </c>
       <c r="K21" s="4"/>
@@ -2615,7 +2636,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"018")</f>
         <v>018</v>
       </c>
       <c r="K22" s="4"/>
@@ -2664,7 +2685,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"019")</f>
         <v>019</v>
       </c>
       <c r="K23" s="4"/>
@@ -2713,7 +2734,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"020")</f>
         <v>020</v>
       </c>
       <c r="K24" s="4"/>
@@ -2762,7 +2783,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"021")</f>
         <v>021</v>
       </c>
       <c r="K25" s="4"/>
@@ -2811,7 +2832,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"022")</f>
         <v>022</v>
       </c>
       <c r="K26" s="4"/>
@@ -2860,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"023")</f>
         <v>023</v>
       </c>
       <c r="K27" s="4"/>
@@ -2909,7 +2930,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"024")</f>
         <v>024</v>
       </c>
       <c r="K28" s="4"/>
@@ -2958,7 +2979,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"025")</f>
         <v>025</v>
       </c>
       <c r="K29" s="4"/>
@@ -3007,7 +3028,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"026")</f>
         <v>026</v>
       </c>
       <c r="K30" s="4"/>
@@ -3056,7 +3077,7 @@
         <v>17</v>
       </c>
       <c r="J31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"027")</f>
         <v>027</v>
       </c>
       <c r="K31" s="4"/>
@@ -3105,7 +3126,7 @@
         <v>17</v>
       </c>
       <c r="J32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="K32" s="4"/>
@@ -3154,7 +3175,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"029")</f>
         <v>029</v>
       </c>
       <c r="K33" s="4"/>
@@ -3203,7 +3224,7 @@
         <v>17</v>
       </c>
       <c r="J34" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"030")</f>
         <v>030</v>
       </c>
       <c r="K34" s="4"/>
@@ -3252,7 +3273,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K35" s="4"/>
@@ -3301,7 +3322,7 @@
         <v>17</v>
       </c>
       <c r="J36" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K36" s="4"/>
@@ -3350,7 +3371,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"032")</f>
         <v>032</v>
       </c>
       <c r="K37" s="4"/>
@@ -3399,7 +3420,7 @@
         <v>17</v>
       </c>
       <c r="J38" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K38" s="4"/>
@@ -3448,7 +3469,7 @@
         <v>112</v>
       </c>
       <c r="J39" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K39" s="4"/>
@@ -3497,7 +3518,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="K40" s="4"/>
@@ -3546,7 +3567,7 @@
         <v>17</v>
       </c>
       <c r="J41" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"035")</f>
         <v>035</v>
       </c>
       <c r="K41" s="4"/>
@@ -3595,7 +3616,7 @@
         <v>17</v>
       </c>
       <c r="J42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"036")</f>
         <v>036</v>
       </c>
       <c r="K42" s="4"/>
@@ -3644,7 +3665,7 @@
         <v>17</v>
       </c>
       <c r="J43" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K43" s="4"/>
@@ -3693,7 +3714,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K44" s="4"/>
@@ -3742,7 +3763,7 @@
         <v>17</v>
       </c>
       <c r="J45" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K45" s="4"/>
@@ -3791,7 +3812,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"038")</f>
         <v>038</v>
       </c>
       <c r="K46" s="4"/>
@@ -3840,7 +3861,7 @@
         <v>17</v>
       </c>
       <c r="J47" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"039")</f>
         <v>039</v>
       </c>
       <c r="K47" s="4"/>
@@ -3889,7 +3910,7 @@
         <v>17</v>
       </c>
       <c r="J48" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"040")</f>
         <v>040</v>
       </c>
       <c r="K48" s="4"/>
@@ -3938,7 +3959,7 @@
         <v>17</v>
       </c>
       <c r="J49" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"041")</f>
         <v>041</v>
       </c>
       <c r="K49" s="4"/>
@@ -3987,7 +4008,7 @@
         <v>17</v>
       </c>
       <c r="J50" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"042")</f>
         <v>042</v>
       </c>
       <c r="K50" s="4"/>
@@ -4036,7 +4057,7 @@
         <v>17</v>
       </c>
       <c r="J51" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"043")</f>
         <v>043</v>
       </c>
       <c r="K51" s="4"/>
@@ -4085,7 +4106,7 @@
         <v>17</v>
       </c>
       <c r="J52" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"044")</f>
         <v>044</v>
       </c>
       <c r="K52" s="4"/>
@@ -4134,7 +4155,7 @@
         <v>17</v>
       </c>
       <c r="J53" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"045")</f>
         <v>045</v>
       </c>
       <c r="K53" s="4"/>
@@ -4183,7 +4204,7 @@
         <v>17</v>
       </c>
       <c r="J54" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"046")</f>
         <v>046</v>
       </c>
       <c r="K54" s="4"/>
@@ -4232,7 +4253,7 @@
         <v>17</v>
       </c>
       <c r="J55" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"047")</f>
         <v>047</v>
       </c>
       <c r="K55" s="4"/>
@@ -4281,7 +4302,7 @@
         <v>17</v>
       </c>
       <c r="J56" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"048")</f>
         <v>048</v>
       </c>
       <c r="K56" s="4"/>
@@ -4330,7 +4351,7 @@
         <v>17</v>
       </c>
       <c r="J57" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"049")</f>
         <v>049</v>
       </c>
       <c r="K57" s="4"/>
@@ -4379,7 +4400,7 @@
         <v>17</v>
       </c>
       <c r="J58" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"050")</f>
         <v>050</v>
       </c>
       <c r="K58" s="4"/>
@@ -4428,7 +4449,7 @@
         <v>17</v>
       </c>
       <c r="J59" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"051")</f>
         <v>051</v>
       </c>
       <c r="K59" s="4"/>
@@ -4477,7 +4498,7 @@
         <v>17</v>
       </c>
       <c r="J60" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"052")</f>
         <v>052</v>
       </c>
       <c r="K60" s="4"/>
@@ -4526,7 +4547,7 @@
         <v>17</v>
       </c>
       <c r="J61" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="K61" s="4"/>
@@ -4575,7 +4596,7 @@
         <v>17</v>
       </c>
       <c r="J62" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"054")</f>
         <v>054</v>
       </c>
       <c r="K62" s="4"/>
@@ -4624,7 +4645,7 @@
         <v>17</v>
       </c>
       <c r="J63" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"055")</f>
         <v>055</v>
       </c>
       <c r="K63" s="4"/>
@@ -4673,7 +4694,7 @@
         <v>17</v>
       </c>
       <c r="J64" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"056")</f>
         <v>056</v>
       </c>
       <c r="K64" s="4"/>
@@ -4722,7 +4743,7 @@
         <v>17</v>
       </c>
       <c r="J65" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"057")</f>
         <v>057</v>
       </c>
       <c r="K65" s="4"/>
@@ -4771,7 +4792,7 @@
         <v>17</v>
       </c>
       <c r="J66" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"058")</f>
         <v>058</v>
       </c>
       <c r="K66" s="4"/>
@@ -4820,7 +4841,7 @@
         <v>17</v>
       </c>
       <c r="J67" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"059")</f>
         <v>059</v>
       </c>
       <c r="K67" s="4"/>
@@ -4869,7 +4890,7 @@
         <v>17</v>
       </c>
       <c r="J68" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"060")</f>
         <v>060</v>
       </c>
       <c r="K68" s="4"/>
@@ -4918,7 +4939,7 @@
         <v>17</v>
       </c>
       <c r="J69" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"061")</f>
         <v>061</v>
       </c>
       <c r="K69" s="4"/>
@@ -4967,7 +4988,7 @@
         <v>17</v>
       </c>
       <c r="J70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"062")</f>
         <v>062</v>
       </c>
       <c r="K70" s="4"/>
@@ -5016,7 +5037,7 @@
         <v>17</v>
       </c>
       <c r="J71" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"063")</f>
         <v>063</v>
       </c>
       <c r="K71" s="4"/>
@@ -5065,7 +5086,7 @@
         <v>17</v>
       </c>
       <c r="J72" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K72" s="4"/>
@@ -5114,7 +5135,7 @@
         <v>17</v>
       </c>
       <c r="J73" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K73" s="4"/>
@@ -5163,7 +5184,7 @@
         <v>17</v>
       </c>
       <c r="J74" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K74" s="4"/>
@@ -5212,7 +5233,7 @@
         <v>17</v>
       </c>
       <c r="J75" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K75" s="4"/>
@@ -5261,7 +5282,7 @@
         <v>17</v>
       </c>
       <c r="J76" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K76" s="4"/>
@@ -5310,7 +5331,7 @@
         <v>17</v>
       </c>
       <c r="J77" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"065")</f>
         <v>065</v>
       </c>
       <c r="K77" s="4"/>
@@ -5359,7 +5380,7 @@
         <v>17</v>
       </c>
       <c r="J78" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"066")</f>
         <v>066</v>
       </c>
       <c r="K78" s="4"/>
@@ -5408,7 +5429,7 @@
         <v>17</v>
       </c>
       <c r="J79" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"067")</f>
         <v>067</v>
       </c>
       <c r="K79" s="4"/>
@@ -5457,7 +5478,7 @@
         <v>17</v>
       </c>
       <c r="J80" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"068")</f>
         <v>068</v>
       </c>
       <c r="K80" s="4"/>
@@ -5506,7 +5527,7 @@
         <v>218</v>
       </c>
       <c r="J81" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"069")</f>
         <v>069</v>
       </c>
       <c r="K81" s="4"/>
@@ -5555,7 +5576,7 @@
         <v>218</v>
       </c>
       <c r="J82" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"070")</f>
         <v>070</v>
       </c>
       <c r="K82" s="4"/>
@@ -5604,7 +5625,7 @@
         <v>17</v>
       </c>
       <c r="J83" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"071")</f>
         <v>071</v>
       </c>
       <c r="K83" s="4"/>
@@ -5653,7 +5674,7 @@
         <v>17</v>
       </c>
       <c r="J84" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"072")</f>
         <v>072</v>
       </c>
       <c r="K84" s="4"/>
@@ -5702,7 +5723,7 @@
         <v>17</v>
       </c>
       <c r="J85" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"073")</f>
         <v>073</v>
       </c>
       <c r="K85" s="4"/>
@@ -5751,7 +5772,7 @@
         <v>17</v>
       </c>
       <c r="J86" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"074")</f>
         <v>074</v>
       </c>
       <c r="K86" s="4"/>
@@ -5800,7 +5821,7 @@
         <v>17</v>
       </c>
       <c r="J87" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K87" s="4"/>
@@ -5849,7 +5870,7 @@
         <v>17</v>
       </c>
       <c r="J88" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K88" s="4"/>
@@ -5898,7 +5919,7 @@
         <v>17</v>
       </c>
       <c r="J89" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"076")</f>
         <v>076</v>
       </c>
       <c r="K89" s="4"/>
@@ -5947,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="J90" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K90" s="4"/>
@@ -5996,7 +6017,7 @@
         <v>17</v>
       </c>
       <c r="J91" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K91" s="4"/>
@@ -6045,7 +6066,7 @@
         <v>17</v>
       </c>
       <c r="J92" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"078")</f>
         <v>078</v>
       </c>
       <c r="K92" s="4"/>
@@ -6094,7 +6115,7 @@
         <v>17</v>
       </c>
       <c r="J93" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"079")</f>
         <v>079</v>
       </c>
       <c r="K93" s="4"/>
@@ -6143,7 +6164,7 @@
         <v>17</v>
       </c>
       <c r="J94" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"080")</f>
         <v>080</v>
       </c>
       <c r="K94" s="4"/>
@@ -6192,7 +6213,7 @@
         <v>17</v>
       </c>
       <c r="J95" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"081")</f>
         <v>081</v>
       </c>
       <c r="K95" s="4"/>
@@ -6241,7 +6262,7 @@
         <v>17</v>
       </c>
       <c r="J96" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"082")</f>
         <v>082</v>
       </c>
       <c r="K96" s="4"/>
@@ -6290,7 +6311,7 @@
         <v>17</v>
       </c>
       <c r="J97" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"083")</f>
         <v>083</v>
       </c>
       <c r="K97" s="4"/>
@@ -6339,7 +6360,7 @@
         <v>268</v>
       </c>
       <c r="J98" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"084")</f>
         <v>084</v>
       </c>
       <c r="K98" s="4"/>
@@ -6388,7 +6409,7 @@
         <v>218</v>
       </c>
       <c r="J99" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"085")</f>
         <v>085</v>
       </c>
       <c r="K99" s="4"/>
@@ -6437,7 +6458,7 @@
         <v>218</v>
       </c>
       <c r="J100" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"086")</f>
         <v>086</v>
       </c>
       <c r="K100" s="4"/>
@@ -6486,7 +6507,7 @@
         <v>218</v>
       </c>
       <c r="J101" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"087")</f>
         <v>087</v>
       </c>
       <c r="K101" s="4"/>
@@ -6535,7 +6556,7 @@
         <v>218</v>
       </c>
       <c r="J102" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"088")</f>
         <v>088</v>
       </c>
       <c r="K102" s="4"/>
@@ -6584,7 +6605,7 @@
         <v>218</v>
       </c>
       <c r="J103" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"089")</f>
         <v>089</v>
       </c>
       <c r="K103" s="4"/>
@@ -6633,7 +6654,7 @@
         <v>218</v>
       </c>
       <c r="J104" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"090")</f>
         <v>090</v>
       </c>
       <c r="K104" s="4"/>
@@ -6682,7 +6703,7 @@
         <v>218</v>
       </c>
       <c r="J105" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"091")</f>
         <v>091</v>
       </c>
       <c r="K105" s="4"/>
@@ -6731,7 +6752,7 @@
         <v>17</v>
       </c>
       <c r="J106" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"092")</f>
         <v>092</v>
       </c>
       <c r="K106" s="4"/>
@@ -6780,7 +6801,7 @@
         <v>17</v>
       </c>
       <c r="J107" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"093")</f>
         <v>093</v>
       </c>
       <c r="K107" s="4"/>
@@ -6829,7 +6850,7 @@
         <v>17</v>
       </c>
       <c r="J108" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"094")</f>
         <v>094</v>
       </c>
       <c r="K108" s="4"/>
@@ -6878,7 +6899,7 @@
         <v>17</v>
       </c>
       <c r="J109" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"095")</f>
         <v>095</v>
       </c>
       <c r="K109" s="4"/>
@@ -6927,7 +6948,7 @@
         <v>17</v>
       </c>
       <c r="J110" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"096")</f>
         <v>096</v>
       </c>
       <c r="K110" s="4"/>
@@ -6976,7 +6997,7 @@
         <v>17</v>
       </c>
       <c r="J111" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"097")</f>
         <v>097</v>
       </c>
       <c r="K111" s="4"/>
@@ -7025,7 +7046,7 @@
         <v>17</v>
       </c>
       <c r="J112" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"098")</f>
         <v>098</v>
       </c>
       <c r="K112" s="4"/>
@@ -7074,7 +7095,7 @@
         <v>17</v>
       </c>
       <c r="J113" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"099")</f>
         <v>099</v>
       </c>
       <c r="K113" s="4"/>
@@ -7123,7 +7144,7 @@
         <v>17</v>
       </c>
       <c r="J114" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"100")</f>
         <v>100</v>
       </c>
       <c r="K114" s="4"/>
@@ -7172,7 +7193,7 @@
         <v>17</v>
       </c>
       <c r="J115" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"101")</f>
         <v>101</v>
       </c>
       <c r="K115" s="4"/>
@@ -7221,7 +7242,7 @@
         <v>17</v>
       </c>
       <c r="J116" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"102")</f>
         <v>102</v>
       </c>
       <c r="K116" s="4"/>
@@ -7270,7 +7291,7 @@
         <v>17</v>
       </c>
       <c r="J117" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"103")</f>
         <v>103</v>
       </c>
       <c r="K117" s="4"/>
@@ -7319,7 +7340,7 @@
         <v>218</v>
       </c>
       <c r="J118" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"104")</f>
         <v>104</v>
       </c>
       <c r="K118" s="4"/>
@@ -7368,7 +7389,7 @@
         <v>218</v>
       </c>
       <c r="J119" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"105")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"105")</f>
         <v>105</v>
       </c>
       <c r="K119" s="4"/>
@@ -7417,7 +7438,7 @@
         <v>218</v>
       </c>
       <c r="J120" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"106")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"106")</f>
         <v>106</v>
       </c>
       <c r="K120" s="4"/>
@@ -7466,7 +7487,7 @@
         <v>17</v>
       </c>
       <c r="J121" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"107")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"107")</f>
         <v>107</v>
       </c>
       <c r="K121" s="4"/>
@@ -7515,7 +7536,7 @@
         <v>17</v>
       </c>
       <c r="J122" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"108")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"108")</f>
         <v>108</v>
       </c>
       <c r="K122" s="4"/>
@@ -7552,7 +7573,7 @@
         <v>323</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>325</v>
@@ -7564,7 +7585,7 @@
         <v>17</v>
       </c>
       <c r="J123" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"109")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"109")</f>
         <v>109</v>
       </c>
       <c r="K123" s="4"/>
@@ -7613,7 +7634,7 @@
         <v>17</v>
       </c>
       <c r="J124" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"110")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"110")</f>
         <v>110</v>
       </c>
       <c r="K124" s="4"/>
@@ -7662,7 +7683,7 @@
         <v>17</v>
       </c>
       <c r="J125" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"111")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"111")</f>
         <v>111</v>
       </c>
       <c r="K125" s="4"/>
@@ -7699,7 +7720,7 @@
         <v>323</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>331</v>
@@ -7711,7 +7732,7 @@
         <v>17</v>
       </c>
       <c r="J126" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"112")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"112")</f>
         <v>112</v>
       </c>
       <c r="K126" s="4"/>
@@ -7733,34 +7754,34 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>335</v>
+      <c r="D127" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="J127" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"113")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"113")</f>
         <v>113</v>
       </c>
       <c r="K127" s="4"/>
@@ -7782,34 +7803,34 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>335</v>
+      <c r="D128" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="J128" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"114")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"114")</f>
         <v>114</v>
       </c>
       <c r="K128" s="4"/>
@@ -7831,34 +7852,34 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>335</v>
+      <c r="D129" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="J129" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"115")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"115")</f>
         <v>115</v>
       </c>
       <c r="K129" s="4"/>
@@ -7880,19 +7901,19 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>14</v>
@@ -7907,7 +7928,7 @@
         <v>268</v>
       </c>
       <c r="J130" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"116")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"116")</f>
         <v>116</v>
       </c>
       <c r="K130" s="4"/>
@@ -7929,19 +7950,19 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>14</v>
@@ -7956,7 +7977,7 @@
         <v>268</v>
       </c>
       <c r="J131" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"117")</f>
         <v>117</v>
       </c>
       <c r="K131" s="4"/>
@@ -7978,19 +7999,19 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
@@ -8005,7 +8026,7 @@
         <v>268</v>
       </c>
       <c r="J132" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"118")</f>
         <v>118</v>
       </c>
       <c r="K132" s="4"/>
@@ -8027,34 +8048,34 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J133" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"119")</f>
         <v>119</v>
       </c>
       <c r="K133" s="4"/>
@@ -8076,34 +8097,34 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J134" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"120")</f>
         <v>120</v>
       </c>
       <c r="K134" s="4"/>
@@ -8125,34 +8146,34 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J135" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"121")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"121")</f>
         <v>121</v>
       </c>
       <c r="K135" s="4"/>
@@ -8174,34 +8195,34 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J136" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"122")</f>
         <v>122</v>
       </c>
       <c r="K136" s="4"/>
@@ -8223,35 +8244,35 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J137" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
-        <v>122</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"123")</f>
+        <v>123</v>
       </c>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
@@ -8272,35 +8293,35 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J138" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"123")</f>
-        <v>123</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"124")</f>
+        <v>124</v>
       </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
@@ -8321,35 +8342,35 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J139" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
-        <v>124</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
       </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
@@ -8370,35 +8391,35 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G140" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H140" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="H140" s="5" t="s">
-        <v>361</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J140" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
-        <v>124</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
       </c>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
@@ -8419,35 +8440,35 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J141" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
       </c>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
@@ -8468,35 +8489,35 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J142" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"127")</f>
+        <v>127</v>
       </c>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
@@ -8517,35 +8538,35 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J143" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"127")</f>
+        <v>127</v>
       </c>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
@@ -8566,35 +8587,35 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J144" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
+        <v>128</v>
       </c>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
@@ -8615,25 +8636,25 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>370</v>
@@ -8642,8 +8663,8 @@
         <v>268</v>
       </c>
       <c r="J145" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"127")</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
+        <v>128</v>
       </c>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
@@ -8664,35 +8685,35 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J146" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
+        <v>128</v>
       </c>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
@@ -8713,35 +8734,35 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J147" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
+        <v>129</v>
       </c>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
@@ -8761,16 +8782,37 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
+      <c r="A148" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J148" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H148,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"130")</f>
+        <v>130</v>
+      </c>
       <c r="K148" s="4"/>
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
@@ -8789,16 +8831,37 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
+      <c r="A149" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J149" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H149,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
+        <v>129</v>
+      </c>
       <c r="K149" s="4"/>
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
@@ -8817,16 +8880,37 @@
       <c r="Z149" s="4"/>
     </row>
     <row r="150">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
+      <c r="A150" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J150" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H150,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
+        <v>129</v>
+      </c>
       <c r="K150" s="4"/>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -8852,6 +8936,7 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -8935,7 +9020,6 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
@@ -9628,14 +9712,14 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="9"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6"/>
+      <c r="H179" s="6"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -9656,14 +9740,14 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="9"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="6"/>
+      <c r="H180" s="6"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -9684,14 +9768,14 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="9"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6"/>
+      <c r="H181" s="6"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -9964,14 +10048,14 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="4"/>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="4"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
+      <c r="A191" s="9"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
+      <c r="F191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -9992,14 +10076,14 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192">
-      <c r="A192" s="4"/>
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -10020,14 +10104,14 @@
       <c r="Z192" s="4"/>
     </row>
     <row r="193">
-      <c r="A193" s="4"/>
-      <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
-      <c r="D193" s="4"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
@@ -34771,6 +34855,90 @@
       <c r="Y1076" s="4"/>
       <c r="Z1076" s="4"/>
     </row>
+    <row r="1077">
+      <c r="A1077" s="4"/>
+      <c r="B1077" s="4"/>
+      <c r="C1077" s="4"/>
+      <c r="D1077" s="4"/>
+      <c r="E1077" s="4"/>
+      <c r="F1077" s="4"/>
+      <c r="G1077" s="4"/>
+      <c r="H1077" s="4"/>
+      <c r="I1077" s="4"/>
+      <c r="J1077" s="4"/>
+      <c r="K1077" s="4"/>
+      <c r="L1077" s="4"/>
+      <c r="M1077" s="4"/>
+      <c r="N1077" s="4"/>
+      <c r="O1077" s="4"/>
+      <c r="P1077" s="4"/>
+      <c r="Q1077" s="4"/>
+      <c r="R1077" s="4"/>
+      <c r="S1077" s="4"/>
+      <c r="T1077" s="4"/>
+      <c r="U1077" s="4"/>
+      <c r="V1077" s="4"/>
+      <c r="W1077" s="4"/>
+      <c r="X1077" s="4"/>
+      <c r="Y1077" s="4"/>
+      <c r="Z1077" s="4"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="4"/>
+      <c r="B1078" s="4"/>
+      <c r="C1078" s="4"/>
+      <c r="D1078" s="4"/>
+      <c r="E1078" s="4"/>
+      <c r="F1078" s="4"/>
+      <c r="G1078" s="4"/>
+      <c r="H1078" s="4"/>
+      <c r="I1078" s="4"/>
+      <c r="J1078" s="4"/>
+      <c r="K1078" s="4"/>
+      <c r="L1078" s="4"/>
+      <c r="M1078" s="4"/>
+      <c r="N1078" s="4"/>
+      <c r="O1078" s="4"/>
+      <c r="P1078" s="4"/>
+      <c r="Q1078" s="4"/>
+      <c r="R1078" s="4"/>
+      <c r="S1078" s="4"/>
+      <c r="T1078" s="4"/>
+      <c r="U1078" s="4"/>
+      <c r="V1078" s="4"/>
+      <c r="W1078" s="4"/>
+      <c r="X1078" s="4"/>
+      <c r="Y1078" s="4"/>
+      <c r="Z1078" s="4"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="4"/>
+      <c r="B1079" s="4"/>
+      <c r="C1079" s="4"/>
+      <c r="D1079" s="4"/>
+      <c r="E1079" s="4"/>
+      <c r="F1079" s="4"/>
+      <c r="G1079" s="4"/>
+      <c r="H1079" s="4"/>
+      <c r="I1079" s="4"/>
+      <c r="J1079" s="4"/>
+      <c r="K1079" s="4"/>
+      <c r="L1079" s="4"/>
+      <c r="M1079" s="4"/>
+      <c r="N1079" s="4"/>
+      <c r="O1079" s="4"/>
+      <c r="P1079" s="4"/>
+      <c r="Q1079" s="4"/>
+      <c r="R1079" s="4"/>
+      <c r="S1079" s="4"/>
+      <c r="T1079" s="4"/>
+      <c r="U1079" s="4"/>
+      <c r="V1079" s="4"/>
+      <c r="W1079" s="4"/>
+      <c r="X1079" s="4"/>
+      <c r="Y1079" s="4"/>
+      <c r="Z1079" s="4"/>
+    </row>
   </sheetData>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,24 +13,42 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={67b169c8-f19c-46f1-b85b-7ec54da15671}</author>
-    <author>tc={7ae6649a-807e-4015-b38f-37eaa2c6b1fd}</author>
-    <author>tc={c113079d-b908-448c-8b48-45a8dab1b0a2}</author>
-    <author>tc={d8aac47c-72e6-4f10-8ef6-685c6c147d6d}</author>
-    <author>tc={e1469053-c5ab-4df9-9e14-d910d17d7cd4}</author>
-    <author>tc={f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}</author>
+    <author>tc={0ef00560-083a-4164-b87e-cea4144be50c}</author>
+    <author>tc={52a29d16-cb6d-4173-9211-408da42bb557}</author>
+    <author>tc={83cfa3cb-cedc-4759-b3af-abc744bc1e52}</author>
+    <author>tc={884d1266-6bc4-4acc-b8f9-c758350e4f8b}</author>
+    <author>tc={cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}</author>
+    <author>tc={d30f0d53-b74c-4705-a530-a205ecd98901}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{67b169c8-f19c-46f1-b85b-7ec54da15671}" ref="G136">
+    <comment authorId="0" xr:uid="{0ef00560-083a-4164-b87e-cea4144be50c}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Le cambiaron la transversalidad
+	Actualmente cuenta con clasificación Programpatica  E
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{7ae6649a-807e-4015-b38f-37eaa2c6b1fd}" ref="A1">
+    <comment authorId="1" xr:uid="{52a29d16-cb6d-4173-9211-408da42bb557}" ref="H41">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{83cfa3cb-cedc-4759-b3af-abc744bc1e52}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con una clasificación programática con letra E
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{884d1266-6bc4-4acc-b8f9-c758350e4f8b}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,25 +57,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{c113079d-b908-448c-8b48-45a8dab1b0a2}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con clasificación Programpatica  E
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{d8aac47c-72e6-4f10-8ef6-685c6c147d6d}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con una clasificación programática con letra E
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{e1469053-c5ab-4df9-9e14-d910d17d7cd4}" ref="F89">
+    <comment authorId="4" xr:uid="{cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}" ref="F89">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -66,12 +66,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="5" xr:uid="{f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}" ref="H41">
+    <comment authorId="5" xr:uid="{d30f0d53-b74c-4705-a530-a205ecd98901}" ref="G136">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
+	Le cambiaron la transversalidad
 </t>
       </text>
     </comment>
@@ -1263,7 +1263,7 @@
       <name val="Nunito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1282,6 +1282,30 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -1289,7 +1313,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1317,6 +1341,18 @@
     <xf borderId="0" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1338,9 +1374,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{1df09a3f-a647-4871-9c3b-258f0246c161}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{a10f06c8-0ecf-4222-9d57-eabe78a1b637}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{43d2ed8e-763f-48f4-961a-236998fd68ff}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{fb345782-a70e-413a-88f9-2e653440b3d4}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1540,22 +1576,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" id="{f5d0ace6-1746-4aa5-80ff-54ef08efbbb5}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{43d2ed8e-763f-48f4-961a-236998fd68ff}" id="{52a29d16-cb6d-4173-9211-408da42bb557}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{e1469053-c5ab-4df9-9e14-d910d17d7cd4}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{9fb36d3d-cc5f-4b7d-b7c3-8c261f66ef1d}" id="{7ae6649a-807e-4015-b38f-37eaa2c6b1fd}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{43d2ed8e-763f-48f4-961a-236998fd68ff}" id="{884d1266-6bc4-4acc-b8f9-c758350e4f8b}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G136" dT="2026-08-03T23:05:51.00" personId="{a10f06c8-0ecf-4222-9d57-eabe78a1b637}" id="{67b169c8-f19c-46f1-b85b-7ec54da15671}" done="0">
+  <x18tc:threadedComment ref="G136" dT="2026-08-03T23:05:51.00" personId="{fb345782-a70e-413a-88f9-2e653440b3d4}" id="{d30f0d53-b74c-4705-a530-a205ecd98901}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{c113079d-b908-448c-8b48-45a8dab1b0a2}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{0ef00560-083a-4164-b87e-cea4144be50c}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{1df09a3f-a647-4871-9c3b-258f0246c161}" id="{d8aac47c-72e6-4f10-8ef6-685c6c147d6d}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{83cfa3cb-cedc-4759-b3af-abc744bc1e52}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -7575,10 +7611,10 @@
       <c r="F123" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G123" s="5" t="s">
+      <c r="G123" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="H123" s="5" t="s">
+      <c r="H123" s="10" t="s">
         <v>326</v>
       </c>
       <c r="I123" s="5" t="s">
@@ -7624,7 +7660,7 @@
       <c r="F124" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G124" s="5" t="s">
+      <c r="G124" s="9" t="s">
         <v>327</v>
       </c>
       <c r="H124" s="5" t="s">
@@ -7673,10 +7709,10 @@
       <c r="F125" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="G125" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="H125" s="5" t="s">
+      <c r="H125" s="11" t="s">
         <v>330</v>
       </c>
       <c r="I125" s="5" t="s">
@@ -7722,7 +7758,7 @@
       <c r="F126" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="G126" s="12" t="s">
         <v>331</v>
       </c>
       <c r="H126" s="5" t="s">
@@ -7771,7 +7807,7 @@
       <c r="F127" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="5" t="s">
+      <c r="G127" s="12" t="s">
         <v>333</v>
       </c>
       <c r="H127" s="5" t="s">
@@ -7820,7 +7856,7 @@
       <c r="F128" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="12" t="s">
         <v>335</v>
       </c>
       <c r="H128" s="5" t="s">
@@ -7869,7 +7905,7 @@
       <c r="F129" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G129" s="5" t="s">
+      <c r="G129" s="9" t="s">
         <v>337</v>
       </c>
       <c r="H129" s="5" t="s">
@@ -9796,14 +9832,14 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="9"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
+      <c r="A182" s="13"/>
+      <c r="B182" s="13"/>
+      <c r="C182" s="13"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="13"/>
+      <c r="F182" s="13"/>
+      <c r="G182" s="13"/>
+      <c r="H182" s="13"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -9824,14 +9860,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="9"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="9"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="9"/>
+      <c r="A183" s="13"/>
+      <c r="B183" s="13"/>
+      <c r="C183" s="13"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="13"/>
+      <c r="F183" s="13"/>
+      <c r="G183" s="13"/>
+      <c r="H183" s="13"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -9852,14 +9888,14 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="9"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="9"/>
+      <c r="A184" s="13"/>
+      <c r="B184" s="13"/>
+      <c r="C184" s="13"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="13"/>
+      <c r="F184" s="13"/>
+      <c r="G184" s="13"/>
+      <c r="H184" s="13"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -9880,14 +9916,14 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="9"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="9"/>
+      <c r="A185" s="13"/>
+      <c r="B185" s="13"/>
+      <c r="C185" s="13"/>
+      <c r="D185" s="13"/>
+      <c r="E185" s="13"/>
+      <c r="F185" s="13"/>
+      <c r="G185" s="13"/>
+      <c r="H185" s="13"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -9908,14 +9944,14 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="9"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
+      <c r="A186" s="13"/>
+      <c r="B186" s="13"/>
+      <c r="C186" s="13"/>
+      <c r="D186" s="13"/>
+      <c r="E186" s="13"/>
+      <c r="F186" s="13"/>
+      <c r="G186" s="13"/>
+      <c r="H186" s="13"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -9936,14 +9972,14 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="9"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="9"/>
+      <c r="A187" s="13"/>
+      <c r="B187" s="13"/>
+      <c r="C187" s="13"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="13"/>
+      <c r="G187" s="13"/>
+      <c r="H187" s="13"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -9964,14 +10000,14 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="9"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
+      <c r="A188" s="13"/>
+      <c r="B188" s="13"/>
+      <c r="C188" s="13"/>
+      <c r="D188" s="13"/>
+      <c r="E188" s="13"/>
+      <c r="F188" s="13"/>
+      <c r="G188" s="13"/>
+      <c r="H188" s="13"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -9992,14 +10028,14 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="9"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
+      <c r="A189" s="13"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -10020,14 +10056,14 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
+      <c r="A190" s="13"/>
+      <c r="B190" s="13"/>
+      <c r="C190" s="13"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="13"/>
+      <c r="F190" s="13"/>
+      <c r="G190" s="13"/>
+      <c r="H190" s="13"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -10048,14 +10084,14 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="9"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
-      <c r="E191" s="9"/>
-      <c r="F191" s="9"/>
-      <c r="G191" s="9"/>
-      <c r="H191" s="9"/>
+      <c r="A191" s="13"/>
+      <c r="B191" s="13"/>
+      <c r="C191" s="13"/>
+      <c r="D191" s="13"/>
+      <c r="E191" s="13"/>
+      <c r="F191" s="13"/>
+      <c r="G191" s="13"/>
+      <c r="H191" s="13"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -10076,14 +10112,14 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192">
-      <c r="A192" s="9"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
-      <c r="E192" s="9"/>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
+      <c r="A192" s="13"/>
+      <c r="B192" s="13"/>
+      <c r="C192" s="13"/>
+      <c r="D192" s="13"/>
+      <c r="E192" s="13"/>
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
+      <c r="H192" s="13"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -10104,14 +10140,14 @@
       <c r="Z192" s="4"/>
     </row>
     <row r="193">
-      <c r="A193" s="9"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
-      <c r="F193" s="9"/>
-      <c r="G193" s="9"/>
-      <c r="H193" s="9"/>
+      <c r="A193" s="13"/>
+      <c r="B193" s="13"/>
+      <c r="C193" s="13"/>
+      <c r="D193" s="13"/>
+      <c r="E193" s="13"/>
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
+      <c r="H193" s="13"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,15 +13,15 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={0ef00560-083a-4164-b87e-cea4144be50c}</author>
-    <author>tc={52a29d16-cb6d-4173-9211-408da42bb557}</author>
-    <author>tc={83cfa3cb-cedc-4759-b3af-abc744bc1e52}</author>
-    <author>tc={884d1266-6bc4-4acc-b8f9-c758350e4f8b}</author>
-    <author>tc={cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}</author>
-    <author>tc={d30f0d53-b74c-4705-a530-a205ecd98901}</author>
+    <author>tc={425033de-e9d8-4e9c-8e6e-d2c927526b97}</author>
+    <author>tc={58ae93ca-f919-4ddb-96a0-47803a2b714e}</author>
+    <author>tc={76d69c0b-3279-45e4-a8b6-9fb13074033f}</author>
+    <author>tc={832dc912-a5f2-4c07-91df-ae888562e43e}</author>
+    <author>tc={b2a3e252-0db6-4a5d-928a-4c5ad9083c06}</author>
+    <author>tc={df007e1c-bfdf-4861-a76a-7f613be4b2fe}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{0ef00560-083a-4164-b87e-cea4144be50c}" ref="F18">
+    <comment authorId="0" xr:uid="{425033de-e9d8-4e9c-8e6e-d2c927526b97}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +30,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{52a29d16-cb6d-4173-9211-408da42bb557}" ref="H41">
+    <comment authorId="1" xr:uid="{58ae93ca-f919-4ddb-96a0-47803a2b714e}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{76d69c0b-3279-45e4-a8b6-9fb13074033f}" ref="G133">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Le cambiaron la transversalidad
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{832dc912-a5f2-4c07-91df-ae888562e43e}" ref="H41">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,7 +57,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{83cfa3cb-cedc-4759-b3af-abc744bc1e52}" ref="F18">
+    <comment authorId="4" xr:uid="{b2a3e252-0db6-4a5d-928a-4c5ad9083c06}" ref="F89">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actalmente es un Lineamiento de Operación
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{df007e1c-bfdf-4861-a76a-7f613be4b2fe}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,39 +75,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{884d1266-6bc4-4acc-b8f9-c758350e4f8b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}" ref="F89">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actalmente es un Lineamiento de Operación
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{d30f0d53-b74c-4705-a530-a205ecd98901}" ref="G136">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Le cambiaron la transversalidad
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="373">
   <si>
     <t>UP</t>
   </si>
@@ -1075,27 +1075,6 @@
   </si>
   <si>
     <t>Mejoramiento de Vivienda</t>
-  </si>
-  <si>
-    <t>S5V_C5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viviendas para contribuir a la reducción del déficit habitacional cuantitativo construidas
-</t>
-  </si>
-  <si>
-    <t>S5V_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obras de infraestructura para brindar servicios básicos ejecutadas
-</t>
-  </si>
-  <si>
-    <t>S5V_D6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obras de urbanización con el propósito de generar suelo urbano asequible ejecutadas
-</t>
   </si>
   <si>
     <t>S5V_D2</t>
@@ -1263,7 +1242,7 @@
       <name val="Nunito"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1282,30 +1261,6 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93C47D"/>
-        <bgColor rgb="FF93C47D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6D7A8"/>
-        <bgColor rgb="FFB6D7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -1313,7 +1268,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1341,18 +1296,6 @@
     <xf borderId="0" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1374,9 +1317,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{43d2ed8e-763f-48f4-961a-236998fd68ff}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{fb345782-a70e-413a-88f9-2e653440b3d4}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{f6189abd-4f9c-49ca-804a-31a479a68891}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{3d82ee12-01c8-4876-97ee-a270738b6afc}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1576,22 +1519,22 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{43d2ed8e-763f-48f4-961a-236998fd68ff}" id="{52a29d16-cb6d-4173-9211-408da42bb557}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" id="{832dc912-a5f2-4c07-91df-ae888562e43e}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{cb9ca402-8adb-4f30-b50a-f1e92dd5cca7}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{b2a3e252-0db6-4a5d-928a-4c5ad9083c06}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{43d2ed8e-763f-48f4-961a-236998fd68ff}" id="{884d1266-6bc4-4acc-b8f9-c758350e4f8b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" id="{58ae93ca-f919-4ddb-96a0-47803a2b714e}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G136" dT="2026-08-03T23:05:51.00" personId="{fb345782-a70e-413a-88f9-2e653440b3d4}" id="{d30f0d53-b74c-4705-a530-a205ecd98901}" done="0">
+  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{3d82ee12-01c8-4876-97ee-a270738b6afc}" id="{76d69c0b-3279-45e4-a8b6-9fb13074033f}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{0ef00560-083a-4164-b87e-cea4144be50c}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{425033de-e9d8-4e9c-8e6e-d2c927526b97}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{91d685b6-e65f-4957-8429-e45cc8dc4e31}" id="{83cfa3cb-cedc-4759-b3af-abc744bc1e52}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{df007e1c-bfdf-4861-a76a-7f613be4b2fe}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1692,7 +1635,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K2" s="4"/>
@@ -1741,7 +1684,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K3" s="4"/>
@@ -1790,7 +1733,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K4" s="4"/>
@@ -1839,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"002")</f>
         <v>002</v>
       </c>
       <c r="K5" s="4"/>
@@ -1888,7 +1831,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"003")</f>
         <v>003</v>
       </c>
       <c r="K6" s="4"/>
@@ -1937,7 +1880,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K7" s="4"/>
@@ -1986,7 +1929,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"004")</f>
         <v>004</v>
       </c>
       <c r="K8" s="4"/>
@@ -2035,7 +1978,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"005")</f>
         <v>005</v>
       </c>
       <c r="K9" s="4"/>
@@ -2084,7 +2027,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"006")</f>
         <v>006</v>
       </c>
       <c r="K10" s="4"/>
@@ -2133,7 +2076,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"007")</f>
         <v>007</v>
       </c>
       <c r="K11" s="4"/>
@@ -2182,7 +2125,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"008")</f>
         <v>008</v>
       </c>
       <c r="K12" s="4"/>
@@ -2231,7 +2174,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"009")</f>
         <v>009</v>
       </c>
       <c r="K13" s="4"/>
@@ -2280,7 +2223,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"010")</f>
         <v>010</v>
       </c>
       <c r="K14" s="4"/>
@@ -2329,7 +2272,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"011")</f>
         <v>011</v>
       </c>
       <c r="K15" s="4"/>
@@ -2378,7 +2321,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"012")</f>
         <v>012</v>
       </c>
       <c r="K16" s="4"/>
@@ -2427,7 +2370,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"013")</f>
         <v>013</v>
       </c>
       <c r="K17" s="4"/>
@@ -2476,7 +2419,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"014")</f>
         <v>014</v>
       </c>
       <c r="K18" s="4"/>
@@ -2525,7 +2468,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"015")</f>
         <v>015</v>
       </c>
       <c r="K19" s="4"/>
@@ -2574,7 +2517,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"016")</f>
         <v>016</v>
       </c>
       <c r="K20" s="4"/>
@@ -2623,7 +2566,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"017")</f>
         <v>017</v>
       </c>
       <c r="K21" s="4"/>
@@ -2672,7 +2615,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"018")</f>
         <v>018</v>
       </c>
       <c r="K22" s="4"/>
@@ -2721,7 +2664,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"019")</f>
         <v>019</v>
       </c>
       <c r="K23" s="4"/>
@@ -2770,7 +2713,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"020")</f>
         <v>020</v>
       </c>
       <c r="K24" s="4"/>
@@ -2819,7 +2762,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"021")</f>
         <v>021</v>
       </c>
       <c r="K25" s="4"/>
@@ -2868,7 +2811,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"022")</f>
         <v>022</v>
       </c>
       <c r="K26" s="4"/>
@@ -2917,7 +2860,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"023")</f>
         <v>023</v>
       </c>
       <c r="K27" s="4"/>
@@ -2966,7 +2909,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"024")</f>
         <v>024</v>
       </c>
       <c r="K28" s="4"/>
@@ -3015,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"025")</f>
         <v>025</v>
       </c>
       <c r="K29" s="4"/>
@@ -3064,7 +3007,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"026")</f>
         <v>026</v>
       </c>
       <c r="K30" s="4"/>
@@ -3113,7 +3056,7 @@
         <v>17</v>
       </c>
       <c r="J31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"027")</f>
         <v>027</v>
       </c>
       <c r="K31" s="4"/>
@@ -3162,7 +3105,7 @@
         <v>17</v>
       </c>
       <c r="J32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="K32" s="4"/>
@@ -3211,7 +3154,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"029")</f>
         <v>029</v>
       </c>
       <c r="K33" s="4"/>
@@ -3260,7 +3203,7 @@
         <v>17</v>
       </c>
       <c r="J34" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"030")</f>
         <v>030</v>
       </c>
       <c r="K34" s="4"/>
@@ -3309,7 +3252,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K35" s="4"/>
@@ -3358,7 +3301,7 @@
         <v>17</v>
       </c>
       <c r="J36" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K36" s="4"/>
@@ -3407,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"032")</f>
         <v>032</v>
       </c>
       <c r="K37" s="4"/>
@@ -3456,7 +3399,7 @@
         <v>17</v>
       </c>
       <c r="J38" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K38" s="4"/>
@@ -3505,7 +3448,7 @@
         <v>112</v>
       </c>
       <c r="J39" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K39" s="4"/>
@@ -3554,7 +3497,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="K40" s="4"/>
@@ -3603,7 +3546,7 @@
         <v>17</v>
       </c>
       <c r="J41" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"035")</f>
         <v>035</v>
       </c>
       <c r="K41" s="4"/>
@@ -3652,7 +3595,7 @@
         <v>17</v>
       </c>
       <c r="J42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"036")</f>
         <v>036</v>
       </c>
       <c r="K42" s="4"/>
@@ -3701,7 +3644,7 @@
         <v>17</v>
       </c>
       <c r="J43" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K43" s="4"/>
@@ -3750,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K44" s="4"/>
@@ -3799,7 +3742,7 @@
         <v>17</v>
       </c>
       <c r="J45" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K45" s="4"/>
@@ -3848,7 +3791,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"038")</f>
         <v>038</v>
       </c>
       <c r="K46" s="4"/>
@@ -3897,7 +3840,7 @@
         <v>17</v>
       </c>
       <c r="J47" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"039")</f>
         <v>039</v>
       </c>
       <c r="K47" s="4"/>
@@ -3946,7 +3889,7 @@
         <v>17</v>
       </c>
       <c r="J48" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"040")</f>
         <v>040</v>
       </c>
       <c r="K48" s="4"/>
@@ -3995,7 +3938,7 @@
         <v>17</v>
       </c>
       <c r="J49" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"041")</f>
         <v>041</v>
       </c>
       <c r="K49" s="4"/>
@@ -4044,7 +3987,7 @@
         <v>17</v>
       </c>
       <c r="J50" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"042")</f>
         <v>042</v>
       </c>
       <c r="K50" s="4"/>
@@ -4093,7 +4036,7 @@
         <v>17</v>
       </c>
       <c r="J51" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"043")</f>
         <v>043</v>
       </c>
       <c r="K51" s="4"/>
@@ -4142,7 +4085,7 @@
         <v>17</v>
       </c>
       <c r="J52" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"044")</f>
         <v>044</v>
       </c>
       <c r="K52" s="4"/>
@@ -4191,7 +4134,7 @@
         <v>17</v>
       </c>
       <c r="J53" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"045")</f>
         <v>045</v>
       </c>
       <c r="K53" s="4"/>
@@ -4240,7 +4183,7 @@
         <v>17</v>
       </c>
       <c r="J54" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"046")</f>
         <v>046</v>
       </c>
       <c r="K54" s="4"/>
@@ -4289,7 +4232,7 @@
         <v>17</v>
       </c>
       <c r="J55" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"047")</f>
         <v>047</v>
       </c>
       <c r="K55" s="4"/>
@@ -4338,7 +4281,7 @@
         <v>17</v>
       </c>
       <c r="J56" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"048")</f>
         <v>048</v>
       </c>
       <c r="K56" s="4"/>
@@ -4387,7 +4330,7 @@
         <v>17</v>
       </c>
       <c r="J57" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"049")</f>
         <v>049</v>
       </c>
       <c r="K57" s="4"/>
@@ -4436,7 +4379,7 @@
         <v>17</v>
       </c>
       <c r="J58" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"050")</f>
         <v>050</v>
       </c>
       <c r="K58" s="4"/>
@@ -4485,7 +4428,7 @@
         <v>17</v>
       </c>
       <c r="J59" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"051")</f>
         <v>051</v>
       </c>
       <c r="K59" s="4"/>
@@ -4534,7 +4477,7 @@
         <v>17</v>
       </c>
       <c r="J60" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"052")</f>
         <v>052</v>
       </c>
       <c r="K60" s="4"/>
@@ -4583,7 +4526,7 @@
         <v>17</v>
       </c>
       <c r="J61" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="K61" s="4"/>
@@ -4632,7 +4575,7 @@
         <v>17</v>
       </c>
       <c r="J62" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"054")</f>
         <v>054</v>
       </c>
       <c r="K62" s="4"/>
@@ -4681,7 +4624,7 @@
         <v>17</v>
       </c>
       <c r="J63" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"055")</f>
         <v>055</v>
       </c>
       <c r="K63" s="4"/>
@@ -4730,7 +4673,7 @@
         <v>17</v>
       </c>
       <c r="J64" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"056")</f>
         <v>056</v>
       </c>
       <c r="K64" s="4"/>
@@ -4779,7 +4722,7 @@
         <v>17</v>
       </c>
       <c r="J65" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"057")</f>
         <v>057</v>
       </c>
       <c r="K65" s="4"/>
@@ -4828,7 +4771,7 @@
         <v>17</v>
       </c>
       <c r="J66" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"058")</f>
         <v>058</v>
       </c>
       <c r="K66" s="4"/>
@@ -4877,7 +4820,7 @@
         <v>17</v>
       </c>
       <c r="J67" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"059")</f>
         <v>059</v>
       </c>
       <c r="K67" s="4"/>
@@ -4926,7 +4869,7 @@
         <v>17</v>
       </c>
       <c r="J68" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"060")</f>
         <v>060</v>
       </c>
       <c r="K68" s="4"/>
@@ -4975,7 +4918,7 @@
         <v>17</v>
       </c>
       <c r="J69" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"061")</f>
         <v>061</v>
       </c>
       <c r="K69" s="4"/>
@@ -5024,7 +4967,7 @@
         <v>17</v>
       </c>
       <c r="J70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"062")</f>
         <v>062</v>
       </c>
       <c r="K70" s="4"/>
@@ -5073,7 +5016,7 @@
         <v>17</v>
       </c>
       <c r="J71" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"063")</f>
         <v>063</v>
       </c>
       <c r="K71" s="4"/>
@@ -5122,7 +5065,7 @@
         <v>17</v>
       </c>
       <c r="J72" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K72" s="4"/>
@@ -5171,7 +5114,7 @@
         <v>17</v>
       </c>
       <c r="J73" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K73" s="4"/>
@@ -5220,7 +5163,7 @@
         <v>17</v>
       </c>
       <c r="J74" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K74" s="4"/>
@@ -5269,7 +5212,7 @@
         <v>17</v>
       </c>
       <c r="J75" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K75" s="4"/>
@@ -5318,7 +5261,7 @@
         <v>17</v>
       </c>
       <c r="J76" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K76" s="4"/>
@@ -5367,7 +5310,7 @@
         <v>17</v>
       </c>
       <c r="J77" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"065")</f>
         <v>065</v>
       </c>
       <c r="K77" s="4"/>
@@ -5416,7 +5359,7 @@
         <v>17</v>
       </c>
       <c r="J78" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"066")</f>
         <v>066</v>
       </c>
       <c r="K78" s="4"/>
@@ -5465,7 +5408,7 @@
         <v>17</v>
       </c>
       <c r="J79" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"067")</f>
         <v>067</v>
       </c>
       <c r="K79" s="4"/>
@@ -5514,7 +5457,7 @@
         <v>17</v>
       </c>
       <c r="J80" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"068")</f>
         <v>068</v>
       </c>
       <c r="K80" s="4"/>
@@ -5563,7 +5506,7 @@
         <v>218</v>
       </c>
       <c r="J81" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"069")</f>
         <v>069</v>
       </c>
       <c r="K81" s="4"/>
@@ -5612,7 +5555,7 @@
         <v>218</v>
       </c>
       <c r="J82" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"070")</f>
         <v>070</v>
       </c>
       <c r="K82" s="4"/>
@@ -5661,7 +5604,7 @@
         <v>17</v>
       </c>
       <c r="J83" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"071")</f>
         <v>071</v>
       </c>
       <c r="K83" s="4"/>
@@ -5710,7 +5653,7 @@
         <v>17</v>
       </c>
       <c r="J84" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"072")</f>
         <v>072</v>
       </c>
       <c r="K84" s="4"/>
@@ -5759,7 +5702,7 @@
         <v>17</v>
       </c>
       <c r="J85" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"073")</f>
         <v>073</v>
       </c>
       <c r="K85" s="4"/>
@@ -5808,7 +5751,7 @@
         <v>17</v>
       </c>
       <c r="J86" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"074")</f>
         <v>074</v>
       </c>
       <c r="K86" s="4"/>
@@ -5857,7 +5800,7 @@
         <v>17</v>
       </c>
       <c r="J87" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K87" s="4"/>
@@ -5906,7 +5849,7 @@
         <v>17</v>
       </c>
       <c r="J88" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K88" s="4"/>
@@ -5955,7 +5898,7 @@
         <v>17</v>
       </c>
       <c r="J89" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"076")</f>
         <v>076</v>
       </c>
       <c r="K89" s="4"/>
@@ -6004,7 +5947,7 @@
         <v>17</v>
       </c>
       <c r="J90" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K90" s="4"/>
@@ -6053,7 +5996,7 @@
         <v>17</v>
       </c>
       <c r="J91" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K91" s="4"/>
@@ -6102,7 +6045,7 @@
         <v>17</v>
       </c>
       <c r="J92" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"078")</f>
         <v>078</v>
       </c>
       <c r="K92" s="4"/>
@@ -6151,7 +6094,7 @@
         <v>17</v>
       </c>
       <c r="J93" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"079")</f>
         <v>079</v>
       </c>
       <c r="K93" s="4"/>
@@ -6200,7 +6143,7 @@
         <v>17</v>
       </c>
       <c r="J94" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"080")</f>
         <v>080</v>
       </c>
       <c r="K94" s="4"/>
@@ -6249,7 +6192,7 @@
         <v>17</v>
       </c>
       <c r="J95" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"081")</f>
         <v>081</v>
       </c>
       <c r="K95" s="4"/>
@@ -6298,7 +6241,7 @@
         <v>17</v>
       </c>
       <c r="J96" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"082")</f>
         <v>082</v>
       </c>
       <c r="K96" s="4"/>
@@ -6347,7 +6290,7 @@
         <v>17</v>
       </c>
       <c r="J97" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"083")</f>
         <v>083</v>
       </c>
       <c r="K97" s="4"/>
@@ -6396,7 +6339,7 @@
         <v>268</v>
       </c>
       <c r="J98" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"084")</f>
         <v>084</v>
       </c>
       <c r="K98" s="4"/>
@@ -6445,7 +6388,7 @@
         <v>218</v>
       </c>
       <c r="J99" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"085")</f>
         <v>085</v>
       </c>
       <c r="K99" s="4"/>
@@ -6494,7 +6437,7 @@
         <v>218</v>
       </c>
       <c r="J100" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"086")</f>
         <v>086</v>
       </c>
       <c r="K100" s="4"/>
@@ -6543,7 +6486,7 @@
         <v>218</v>
       </c>
       <c r="J101" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"087")</f>
         <v>087</v>
       </c>
       <c r="K101" s="4"/>
@@ -6592,7 +6535,7 @@
         <v>218</v>
       </c>
       <c r="J102" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"088")</f>
         <v>088</v>
       </c>
       <c r="K102" s="4"/>
@@ -6641,7 +6584,7 @@
         <v>218</v>
       </c>
       <c r="J103" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"089")</f>
         <v>089</v>
       </c>
       <c r="K103" s="4"/>
@@ -6690,7 +6633,7 @@
         <v>218</v>
       </c>
       <c r="J104" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"090")</f>
         <v>090</v>
       </c>
       <c r="K104" s="4"/>
@@ -6739,7 +6682,7 @@
         <v>218</v>
       </c>
       <c r="J105" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"091")</f>
         <v>091</v>
       </c>
       <c r="K105" s="4"/>
@@ -6788,7 +6731,7 @@
         <v>17</v>
       </c>
       <c r="J106" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"092")</f>
         <v>092</v>
       </c>
       <c r="K106" s="4"/>
@@ -6837,7 +6780,7 @@
         <v>17</v>
       </c>
       <c r="J107" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"093")</f>
         <v>093</v>
       </c>
       <c r="K107" s="4"/>
@@ -6886,7 +6829,7 @@
         <v>17</v>
       </c>
       <c r="J108" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"094")</f>
         <v>094</v>
       </c>
       <c r="K108" s="4"/>
@@ -6935,7 +6878,7 @@
         <v>17</v>
       </c>
       <c r="J109" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"095")</f>
         <v>095</v>
       </c>
       <c r="K109" s="4"/>
@@ -6984,7 +6927,7 @@
         <v>17</v>
       </c>
       <c r="J110" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"096")</f>
         <v>096</v>
       </c>
       <c r="K110" s="4"/>
@@ -7033,7 +6976,7 @@
         <v>17</v>
       </c>
       <c r="J111" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"097")</f>
         <v>097</v>
       </c>
       <c r="K111" s="4"/>
@@ -7082,7 +7025,7 @@
         <v>17</v>
       </c>
       <c r="J112" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"098")</f>
         <v>098</v>
       </c>
       <c r="K112" s="4"/>
@@ -7131,7 +7074,7 @@
         <v>17</v>
       </c>
       <c r="J113" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"099")</f>
         <v>099</v>
       </c>
       <c r="K113" s="4"/>
@@ -7180,7 +7123,7 @@
         <v>17</v>
       </c>
       <c r="J114" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"100")</f>
         <v>100</v>
       </c>
       <c r="K114" s="4"/>
@@ -7229,7 +7172,7 @@
         <v>17</v>
       </c>
       <c r="J115" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"101")</f>
         <v>101</v>
       </c>
       <c r="K115" s="4"/>
@@ -7278,7 +7221,7 @@
         <v>17</v>
       </c>
       <c r="J116" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"102")</f>
         <v>102</v>
       </c>
       <c r="K116" s="4"/>
@@ -7327,7 +7270,7 @@
         <v>17</v>
       </c>
       <c r="J117" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"103")</f>
         <v>103</v>
       </c>
       <c r="K117" s="4"/>
@@ -7376,7 +7319,7 @@
         <v>218</v>
       </c>
       <c r="J118" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"104")</f>
         <v>104</v>
       </c>
       <c r="K118" s="4"/>
@@ -7425,7 +7368,7 @@
         <v>218</v>
       </c>
       <c r="J119" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"105")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"105")</f>
         <v>105</v>
       </c>
       <c r="K119" s="4"/>
@@ -7474,7 +7417,7 @@
         <v>218</v>
       </c>
       <c r="J120" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"106")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"106")</f>
         <v>106</v>
       </c>
       <c r="K120" s="4"/>
@@ -7523,7 +7466,7 @@
         <v>17</v>
       </c>
       <c r="J121" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"107")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"107")</f>
         <v>107</v>
       </c>
       <c r="K121" s="4"/>
@@ -7572,7 +7515,7 @@
         <v>17</v>
       </c>
       <c r="J122" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"108")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"108")</f>
         <v>108</v>
       </c>
       <c r="K122" s="4"/>
@@ -7609,19 +7552,19 @@
         <v>323</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G123" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="H123" s="10" t="s">
+      <c r="H123" s="5" t="s">
         <v>326</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J123" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"109")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"109")</f>
         <v>109</v>
       </c>
       <c r="K123" s="4"/>
@@ -7660,7 +7603,7 @@
       <c r="F124" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G124" s="5" t="s">
         <v>327</v>
       </c>
       <c r="H124" s="5" t="s">
@@ -7670,7 +7613,7 @@
         <v>17</v>
       </c>
       <c r="J124" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"110")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"110")</f>
         <v>110</v>
       </c>
       <c r="K124" s="4"/>
@@ -7709,17 +7652,17 @@
       <c r="F125" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G125" s="9" t="s">
+      <c r="G125" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="H125" s="11" t="s">
+      <c r="H125" s="5" t="s">
         <v>330</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J125" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"111")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"111")</f>
         <v>111</v>
       </c>
       <c r="K125" s="4"/>
@@ -7756,9 +7699,9 @@
         <v>323</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G126" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G126" s="5" t="s">
         <v>331</v>
       </c>
       <c r="H126" s="5" t="s">
@@ -7768,7 +7711,7 @@
         <v>17</v>
       </c>
       <c r="J126" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"112")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"112")</f>
         <v>112</v>
       </c>
       <c r="K126" s="4"/>
@@ -7790,34 +7733,34 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D127" s="6" t="s">
-        <v>324</v>
+      <c r="D127" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G127" s="12" t="s">
-        <v>333</v>
+      <c r="G127" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="J127" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"113")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"113")</f>
         <v>113</v>
       </c>
       <c r="K127" s="4"/>
@@ -7839,34 +7782,34 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D128" s="6" t="s">
-        <v>324</v>
+      <c r="D128" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G128" s="12" t="s">
-        <v>335</v>
+      <c r="G128" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="J128" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"114")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"114")</f>
         <v>114</v>
       </c>
       <c r="K128" s="4"/>
@@ -7888,34 +7831,34 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D129" s="6" t="s">
-        <v>324</v>
+      <c r="D129" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G129" s="9" t="s">
-        <v>337</v>
+      <c r="G129" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="J129" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"115")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"115")</f>
         <v>115</v>
       </c>
       <c r="K129" s="4"/>
@@ -7937,19 +7880,19 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>14</v>
@@ -7964,7 +7907,7 @@
         <v>268</v>
       </c>
       <c r="J130" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"116")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"116")</f>
         <v>116</v>
       </c>
       <c r="K130" s="4"/>
@@ -7986,19 +7929,19 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>14</v>
@@ -8013,7 +7956,7 @@
         <v>268</v>
       </c>
       <c r="J131" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"117")</f>
         <v>117</v>
       </c>
       <c r="K131" s="4"/>
@@ -8035,19 +7978,19 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
@@ -8062,7 +8005,7 @@
         <v>268</v>
       </c>
       <c r="J132" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"118")</f>
         <v>118</v>
       </c>
       <c r="K132" s="4"/>
@@ -8084,34 +8027,34 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G133" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H133" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="H133" s="5" t="s">
-        <v>349</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J133" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"119")</f>
         <v>119</v>
       </c>
       <c r="K133" s="4"/>
@@ -8133,34 +8076,34 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J134" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"120")</f>
         <v>120</v>
       </c>
       <c r="K134" s="4"/>
@@ -8182,34 +8125,34 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J135" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"121")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"121")</f>
         <v>121</v>
       </c>
       <c r="K135" s="4"/>
@@ -8231,34 +8174,34 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J136" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"122")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
         <v>122</v>
       </c>
       <c r="K136" s="4"/>
@@ -8280,35 +8223,35 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J137" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"123")</f>
-        <v>123</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
+        <v>122</v>
       </c>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
@@ -8329,35 +8272,35 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J138" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"124")</f>
-        <v>124</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"123")</f>
+        <v>123</v>
       </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
@@ -8378,35 +8321,35 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G139" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H139" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J139" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
+        <v>124</v>
       </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
@@ -8427,35 +8370,35 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J140" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
+        <v>124</v>
       </c>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
@@ -8476,35 +8419,35 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G141" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H141" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="H141" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J141" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
       </c>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
@@ -8525,35 +8468,35 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J142" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"127")</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
       </c>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
@@ -8574,35 +8517,35 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J143" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"127")</f>
-        <v>127</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
+        <v>125</v>
       </c>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
@@ -8623,35 +8566,35 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J144" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
       </c>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
@@ -8672,25 +8615,25 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>370</v>
@@ -8699,8 +8642,8 @@
         <v>268</v>
       </c>
       <c r="J145" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"127")</f>
+        <v>127</v>
       </c>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
@@ -8721,35 +8664,35 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J146" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"128")</f>
-        <v>128</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
       </c>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
@@ -8770,35 +8713,35 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J147" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
-        <v>129</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
+        <v>126</v>
       </c>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
@@ -8818,37 +8761,16 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="H148" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="I148" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J148" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H148,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"130")</f>
-        <v>130</v>
-      </c>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+      <c r="H148" s="6"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
       <c r="K148" s="4"/>
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
@@ -8867,37 +8789,16 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="I149" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J149" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H149,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
-        <v>129</v>
-      </c>
+      <c r="A149" s="6"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
       <c r="K149" s="4"/>
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
@@ -8916,37 +8817,16 @@
       <c r="Z149" s="4"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="I150" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J150" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H150,UNIQUE(FILTER($H$2:$H1079,$H$2:$H1079&lt;&gt;"""")),0),""000"")"),"129")</f>
-        <v>129</v>
-      </c>
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="6"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
       <c r="K150" s="4"/>
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
@@ -8972,7 +8852,6 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -9056,6 +8935,7 @@
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
+      <c r="H154" s="6"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
@@ -9748,14 +9628,14 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -9776,14 +9656,14 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -9804,14 +9684,14 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -9832,14 +9712,14 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="13"/>
-      <c r="B182" s="13"/>
-      <c r="C182" s="13"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
-      <c r="G182" s="13"/>
-      <c r="H182" s="13"/>
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -9860,14 +9740,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="13"/>
-      <c r="B183" s="13"/>
-      <c r="C183" s="13"/>
-      <c r="D183" s="13"/>
-      <c r="E183" s="13"/>
-      <c r="F183" s="13"/>
-      <c r="G183" s="13"/>
-      <c r="H183" s="13"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -9888,14 +9768,14 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="13"/>
-      <c r="B184" s="13"/>
-      <c r="C184" s="13"/>
-      <c r="D184" s="13"/>
-      <c r="E184" s="13"/>
-      <c r="F184" s="13"/>
-      <c r="G184" s="13"/>
-      <c r="H184" s="13"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
+      <c r="F184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -9916,14 +9796,14 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="13"/>
-      <c r="B185" s="13"/>
-      <c r="C185" s="13"/>
-      <c r="D185" s="13"/>
-      <c r="E185" s="13"/>
-      <c r="F185" s="13"/>
-      <c r="G185" s="13"/>
-      <c r="H185" s="13"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -9944,14 +9824,14 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="13"/>
-      <c r="B186" s="13"/>
-      <c r="C186" s="13"/>
-      <c r="D186" s="13"/>
-      <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -9972,14 +9852,14 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="13"/>
-      <c r="B187" s="13"/>
-      <c r="C187" s="13"/>
-      <c r="D187" s="13"/>
-      <c r="E187" s="13"/>
-      <c r="F187" s="13"/>
-      <c r="G187" s="13"/>
-      <c r="H187" s="13"/>
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -10000,14 +9880,14 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="13"/>
-      <c r="B188" s="13"/>
-      <c r="C188" s="13"/>
-      <c r="D188" s="13"/>
-      <c r="E188" s="13"/>
-      <c r="F188" s="13"/>
-      <c r="G188" s="13"/>
-      <c r="H188" s="13"/>
+      <c r="A188" s="9"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -10028,14 +9908,14 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="13"/>
-      <c r="B189" s="13"/>
-      <c r="C189" s="13"/>
-      <c r="D189" s="13"/>
-      <c r="E189" s="13"/>
-      <c r="F189" s="13"/>
-      <c r="G189" s="13"/>
-      <c r="H189" s="13"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -10056,14 +9936,14 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="13"/>
-      <c r="B190" s="13"/>
-      <c r="C190" s="13"/>
-      <c r="D190" s="13"/>
-      <c r="E190" s="13"/>
-      <c r="F190" s="13"/>
-      <c r="G190" s="13"/>
-      <c r="H190" s="13"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -10084,14 +9964,14 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191">
-      <c r="A191" s="13"/>
-      <c r="B191" s="13"/>
-      <c r="C191" s="13"/>
-      <c r="D191" s="13"/>
-      <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
-      <c r="G191" s="13"/>
-      <c r="H191" s="13"/>
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -10112,14 +9992,14 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192">
-      <c r="A192" s="13"/>
-      <c r="B192" s="13"/>
-      <c r="C192" s="13"/>
-      <c r="D192" s="13"/>
-      <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
-      <c r="G192" s="13"/>
-      <c r="H192" s="13"/>
+      <c r="A192" s="4"/>
+      <c r="B192" s="4"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -10140,14 +10020,14 @@
       <c r="Z192" s="4"/>
     </row>
     <row r="193">
-      <c r="A193" s="13"/>
-      <c r="B193" s="13"/>
-      <c r="C193" s="13"/>
-      <c r="D193" s="13"/>
-      <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
-      <c r="G193" s="13"/>
-      <c r="H193" s="13"/>
+      <c r="A193" s="4"/>
+      <c r="B193" s="4"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
@@ -34891,90 +34771,6 @@
       <c r="Y1076" s="4"/>
       <c r="Z1076" s="4"/>
     </row>
-    <row r="1077">
-      <c r="A1077" s="4"/>
-      <c r="B1077" s="4"/>
-      <c r="C1077" s="4"/>
-      <c r="D1077" s="4"/>
-      <c r="E1077" s="4"/>
-      <c r="F1077" s="4"/>
-      <c r="G1077" s="4"/>
-      <c r="H1077" s="4"/>
-      <c r="I1077" s="4"/>
-      <c r="J1077" s="4"/>
-      <c r="K1077" s="4"/>
-      <c r="L1077" s="4"/>
-      <c r="M1077" s="4"/>
-      <c r="N1077" s="4"/>
-      <c r="O1077" s="4"/>
-      <c r="P1077" s="4"/>
-      <c r="Q1077" s="4"/>
-      <c r="R1077" s="4"/>
-      <c r="S1077" s="4"/>
-      <c r="T1077" s="4"/>
-      <c r="U1077" s="4"/>
-      <c r="V1077" s="4"/>
-      <c r="W1077" s="4"/>
-      <c r="X1077" s="4"/>
-      <c r="Y1077" s="4"/>
-      <c r="Z1077" s="4"/>
-    </row>
-    <row r="1078">
-      <c r="A1078" s="4"/>
-      <c r="B1078" s="4"/>
-      <c r="C1078" s="4"/>
-      <c r="D1078" s="4"/>
-      <c r="E1078" s="4"/>
-      <c r="F1078" s="4"/>
-      <c r="G1078" s="4"/>
-      <c r="H1078" s="4"/>
-      <c r="I1078" s="4"/>
-      <c r="J1078" s="4"/>
-      <c r="K1078" s="4"/>
-      <c r="L1078" s="4"/>
-      <c r="M1078" s="4"/>
-      <c r="N1078" s="4"/>
-      <c r="O1078" s="4"/>
-      <c r="P1078" s="4"/>
-      <c r="Q1078" s="4"/>
-      <c r="R1078" s="4"/>
-      <c r="S1078" s="4"/>
-      <c r="T1078" s="4"/>
-      <c r="U1078" s="4"/>
-      <c r="V1078" s="4"/>
-      <c r="W1078" s="4"/>
-      <c r="X1078" s="4"/>
-      <c r="Y1078" s="4"/>
-      <c r="Z1078" s="4"/>
-    </row>
-    <row r="1079">
-      <c r="A1079" s="4"/>
-      <c r="B1079" s="4"/>
-      <c r="C1079" s="4"/>
-      <c r="D1079" s="4"/>
-      <c r="E1079" s="4"/>
-      <c r="F1079" s="4"/>
-      <c r="G1079" s="4"/>
-      <c r="H1079" s="4"/>
-      <c r="I1079" s="4"/>
-      <c r="J1079" s="4"/>
-      <c r="K1079" s="4"/>
-      <c r="L1079" s="4"/>
-      <c r="M1079" s="4"/>
-      <c r="N1079" s="4"/>
-      <c r="O1079" s="4"/>
-      <c r="P1079" s="4"/>
-      <c r="Q1079" s="4"/>
-      <c r="R1079" s="4"/>
-      <c r="S1079" s="4"/>
-      <c r="T1079" s="4"/>
-      <c r="U1079" s="4"/>
-      <c r="V1079" s="4"/>
-      <c r="W1079" s="4"/>
-      <c r="X1079" s="4"/>
-      <c r="Y1079" s="4"/>
-      <c r="Z1079" s="4"/>
-    </row>
   </sheetData>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,15 +13,26 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={425033de-e9d8-4e9c-8e6e-d2c927526b97}</author>
-    <author>tc={58ae93ca-f919-4ddb-96a0-47803a2b714e}</author>
-    <author>tc={76d69c0b-3279-45e4-a8b6-9fb13074033f}</author>
-    <author>tc={832dc912-a5f2-4c07-91df-ae888562e43e}</author>
-    <author>tc={b2a3e252-0db6-4a5d-928a-4c5ad9083c06}</author>
-    <author>tc={df007e1c-bfdf-4861-a76a-7f613be4b2fe}</author>
+    <author>tc={04545d8b-8847-49cf-8bac-f4dfbabfeb4a}</author>
+    <author>tc={14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}</author>
+    <author>tc={84478949-6a9b-4a11-a54e-89080d944ab9}</author>
+    <author>tc={8f6204b8-4fa0-4319-9ed2-65baaaad30d6}</author>
+    <author>tc={b513cf22-f97e-4149-befb-1089378921cd}</author>
+    <author>tc={bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}</author>
+    <author>tc={d81b8a74-c48a-4dea-86a7-de993678a0f8}</author>
+    <author>tc={eb8ff5e1-0a62-4485-8ff7-247a481aae65}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{425033de-e9d8-4e9c-8e6e-d2c927526b97}" ref="F18">
+    <comment authorId="0" xr:uid="{04545d8b-8847-49cf-8bac-f4dfbabfeb4a}" ref="F89">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actalmente es un Lineamiento de Operación
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +41,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{58ae93ca-f919-4ddb-96a0-47803a2b714e}" ref="A1">
+    <comment authorId="2" xr:uid="{84478949-6a9b-4a11-a54e-89080d944ab9}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,7 +50,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{76d69c0b-3279-45e4-a8b6-9fb13074033f}" ref="G133">
+    <comment authorId="3" xr:uid="{8f6204b8-4fa0-4319-9ed2-65baaaad30d6}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,7 +59,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{832dc912-a5f2-4c07-91df-ae888562e43e}" ref="H41">
+    <comment authorId="4" xr:uid="{b513cf22-f97e-4149-befb-1089378921cd}" ref="H124">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Tiene recurso propio
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}" ref="F18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Actualmente cuenta con una clasificación programática con letra E
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{d81b8a74-c48a-4dea-86a7-de993678a0f8}" ref="H41">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,21 +86,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{b2a3e252-0db6-4a5d-928a-4c5ad9083c06}" ref="F89">
+    <comment authorId="7" xr:uid="{eb8ff5e1-0a62-4485-8ff7-247a481aae65}" ref="H126">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Actalmente es un Lineamiento de Operación
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{df007e1c-bfdf-4861-a76a-7f613be4b2fe}" ref="F18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Actualmente cuenta con una clasificación programática con letra E
+	Solo tiene recurso propio
 </t>
       </text>
     </comment>
@@ -80,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="362">
   <si>
     <t>UP</t>
   </si>
@@ -1110,33 +1130,15 @@
     <t xml:space="preserve">Becas Talento </t>
   </si>
   <si>
-    <t>SE4_A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becas para hijas e hijos de policías </t>
-  </si>
-  <si>
-    <t>SE4_C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becas para hijas e hijos de militares </t>
-  </si>
-  <si>
     <t>SE6_B4</t>
   </si>
   <si>
     <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
   </si>
   <si>
-    <t>Apoyos económicos a estudiantes en situación de internado de la Escuela Normal de Atequiza otrogados.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ayuda económica para las y los estudiantes del Programa Talento la Estilo Jalisco </t>
   </si>
   <si>
-    <t>Ayuda económica a alumnas en el Internado Beatriz Hernández otorgada.</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -1156,21 +1158,6 @@
   </si>
   <si>
     <t>S41_C2</t>
-  </si>
-  <si>
-    <t>S43_C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hecho al Estilo Jalisco </t>
-  </si>
-  <si>
-    <t>S45_C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crece tu Negocio al Estilo Jalisco </t>
-  </si>
-  <si>
-    <t>S45_C2</t>
   </si>
   <si>
     <t>S48_01</t>
@@ -1242,7 +1229,7 @@
       <name val="Nunito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1261,6 +1248,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -1268,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1296,6 +1289,9 @@
     <xf borderId="0" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,9 +1313,10 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{f6189abd-4f9c-49ca-804a-31a479a68891}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{3d82ee12-01c8-4876-97ee-a270738b6afc}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{28e245ef-59ec-4ecf-9243-55a9814940ff}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{46d3832a-6c5c-499e-b76f-e71956d7f64e}" providerId="google-sheets"/>
+  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1519,22 +1516,28 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" id="{832dc912-a5f2-4c07-91df-ae888562e43e}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{28e245ef-59ec-4ecf-9243-55a9814940ff}" id="{d81b8a74-c48a-4dea-86a7-de993678a0f8}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{b2a3e252-0db6-4a5d-928a-4c5ad9083c06}" done="0">
+  <x18tc:threadedComment ref="H126" dT="2026-08-12T23:13:36.00" personId="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" id="{eb8ff5e1-0a62-4485-8ff7-247a481aae65}" done="0">
+    <x18tc:text xml:space="preserve">Solo tiene recurso propio</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{04545d8b-8847-49cf-8bac-f4dfbabfeb4a}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{37f4a8c3-b8a0-480b-9781-e607b4cd58dc}" id="{58ae93ca-f919-4ddb-96a0-47803a2b714e}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{28e245ef-59ec-4ecf-9243-55a9814940ff}" id="{84478949-6a9b-4a11-a54e-89080d944ab9}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G133" dT="2026-08-03T23:05:51.00" personId="{3d82ee12-01c8-4876-97ee-a270738b6afc}" id="{76d69c0b-3279-45e4-a8b6-9fb13074033f}" done="0">
+  <x18tc:threadedComment ref="H124" dT="2026-08-12T23:13:08.00" personId="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" id="{b513cf22-f97e-4149-befb-1089378921cd}" done="0">
+    <x18tc:text xml:space="preserve">Tiene recurso propio</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{46d3832a-6c5c-499e-b76f-e71956d7f64e}" id="{8f6204b8-4fa0-4319-9ed2-65baaaad30d6}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{425033de-e9d8-4e9c-8e6e-d2c927526b97}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{f6189abd-4f9c-49ca-804a-31a479a68891}" id="{df007e1c-bfdf-4861-a76a-7f613be4b2fe}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1635,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K2" s="4"/>
@@ -1684,7 +1687,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K3" s="4"/>
@@ -1733,7 +1736,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K4" s="4"/>
@@ -1782,7 +1785,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"002")</f>
         <v>002</v>
       </c>
       <c r="K5" s="4"/>
@@ -1831,7 +1834,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"003")</f>
         <v>003</v>
       </c>
       <c r="K6" s="4"/>
@@ -1880,7 +1883,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K7" s="4"/>
@@ -1929,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"004")</f>
         <v>004</v>
       </c>
       <c r="K8" s="4"/>
@@ -1978,7 +1981,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"005")</f>
         <v>005</v>
       </c>
       <c r="K9" s="4"/>
@@ -2027,7 +2030,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"006")</f>
         <v>006</v>
       </c>
       <c r="K10" s="4"/>
@@ -2076,7 +2079,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"007")</f>
         <v>007</v>
       </c>
       <c r="K11" s="4"/>
@@ -2125,7 +2128,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"008")</f>
         <v>008</v>
       </c>
       <c r="K12" s="4"/>
@@ -2174,7 +2177,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"009")</f>
         <v>009</v>
       </c>
       <c r="K13" s="4"/>
@@ -2223,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"010")</f>
         <v>010</v>
       </c>
       <c r="K14" s="4"/>
@@ -2272,7 +2275,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"011")</f>
         <v>011</v>
       </c>
       <c r="K15" s="4"/>
@@ -2321,7 +2324,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"012")</f>
         <v>012</v>
       </c>
       <c r="K16" s="4"/>
@@ -2370,7 +2373,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"013")</f>
         <v>013</v>
       </c>
       <c r="K17" s="4"/>
@@ -2419,7 +2422,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"014")</f>
         <v>014</v>
       </c>
       <c r="K18" s="4"/>
@@ -2468,7 +2471,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"015")</f>
         <v>015</v>
       </c>
       <c r="K19" s="4"/>
@@ -2517,7 +2520,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"016")</f>
         <v>016</v>
       </c>
       <c r="K20" s="4"/>
@@ -2566,7 +2569,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"017")</f>
         <v>017</v>
       </c>
       <c r="K21" s="4"/>
@@ -2615,7 +2618,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"018")</f>
         <v>018</v>
       </c>
       <c r="K22" s="4"/>
@@ -2664,7 +2667,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"019")</f>
         <v>019</v>
       </c>
       <c r="K23" s="4"/>
@@ -2713,7 +2716,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"020")</f>
         <v>020</v>
       </c>
       <c r="K24" s="4"/>
@@ -2762,7 +2765,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"021")</f>
         <v>021</v>
       </c>
       <c r="K25" s="4"/>
@@ -2811,7 +2814,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"022")</f>
         <v>022</v>
       </c>
       <c r="K26" s="4"/>
@@ -2860,7 +2863,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"023")</f>
         <v>023</v>
       </c>
       <c r="K27" s="4"/>
@@ -2909,7 +2912,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"024")</f>
         <v>024</v>
       </c>
       <c r="K28" s="4"/>
@@ -2958,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"025")</f>
         <v>025</v>
       </c>
       <c r="K29" s="4"/>
@@ -3007,7 +3010,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"026")</f>
         <v>026</v>
       </c>
       <c r="K30" s="4"/>
@@ -3056,7 +3059,7 @@
         <v>17</v>
       </c>
       <c r="J31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"027")</f>
         <v>027</v>
       </c>
       <c r="K31" s="4"/>
@@ -3105,7 +3108,7 @@
         <v>17</v>
       </c>
       <c r="J32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="K32" s="4"/>
@@ -3154,7 +3157,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"029")</f>
         <v>029</v>
       </c>
       <c r="K33" s="4"/>
@@ -3203,7 +3206,7 @@
         <v>17</v>
       </c>
       <c r="J34" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"030")</f>
         <v>030</v>
       </c>
       <c r="K34" s="4"/>
@@ -3252,7 +3255,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K35" s="4"/>
@@ -3301,7 +3304,7 @@
         <v>17</v>
       </c>
       <c r="J36" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K36" s="4"/>
@@ -3350,7 +3353,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"032")</f>
         <v>032</v>
       </c>
       <c r="K37" s="4"/>
@@ -3399,7 +3402,7 @@
         <v>17</v>
       </c>
       <c r="J38" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K38" s="4"/>
@@ -3448,7 +3451,7 @@
         <v>112</v>
       </c>
       <c r="J39" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K39" s="4"/>
@@ -3497,7 +3500,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="K40" s="4"/>
@@ -3546,7 +3549,7 @@
         <v>17</v>
       </c>
       <c r="J41" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"035")</f>
         <v>035</v>
       </c>
       <c r="K41" s="4"/>
@@ -3595,7 +3598,7 @@
         <v>17</v>
       </c>
       <c r="J42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"036")</f>
         <v>036</v>
       </c>
       <c r="K42" s="4"/>
@@ -3644,7 +3647,7 @@
         <v>17</v>
       </c>
       <c r="J43" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K43" s="4"/>
@@ -3693,7 +3696,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K44" s="4"/>
@@ -3742,7 +3745,7 @@
         <v>17</v>
       </c>
       <c r="J45" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K45" s="4"/>
@@ -3791,7 +3794,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"038")</f>
         <v>038</v>
       </c>
       <c r="K46" s="4"/>
@@ -3840,7 +3843,7 @@
         <v>17</v>
       </c>
       <c r="J47" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"039")</f>
         <v>039</v>
       </c>
       <c r="K47" s="4"/>
@@ -3889,7 +3892,7 @@
         <v>17</v>
       </c>
       <c r="J48" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"040")</f>
         <v>040</v>
       </c>
       <c r="K48" s="4"/>
@@ -3938,7 +3941,7 @@
         <v>17</v>
       </c>
       <c r="J49" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"041")</f>
         <v>041</v>
       </c>
       <c r="K49" s="4"/>
@@ -3987,7 +3990,7 @@
         <v>17</v>
       </c>
       <c r="J50" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"042")</f>
         <v>042</v>
       </c>
       <c r="K50" s="4"/>
@@ -4036,7 +4039,7 @@
         <v>17</v>
       </c>
       <c r="J51" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"043")</f>
         <v>043</v>
       </c>
       <c r="K51" s="4"/>
@@ -4085,7 +4088,7 @@
         <v>17</v>
       </c>
       <c r="J52" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"044")</f>
         <v>044</v>
       </c>
       <c r="K52" s="4"/>
@@ -4134,7 +4137,7 @@
         <v>17</v>
       </c>
       <c r="J53" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"045")</f>
         <v>045</v>
       </c>
       <c r="K53" s="4"/>
@@ -4183,7 +4186,7 @@
         <v>17</v>
       </c>
       <c r="J54" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"046")</f>
         <v>046</v>
       </c>
       <c r="K54" s="4"/>
@@ -4232,7 +4235,7 @@
         <v>17</v>
       </c>
       <c r="J55" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"047")</f>
         <v>047</v>
       </c>
       <c r="K55" s="4"/>
@@ -4281,7 +4284,7 @@
         <v>17</v>
       </c>
       <c r="J56" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"048")</f>
         <v>048</v>
       </c>
       <c r="K56" s="4"/>
@@ -4330,7 +4333,7 @@
         <v>17</v>
       </c>
       <c r="J57" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"049")</f>
         <v>049</v>
       </c>
       <c r="K57" s="4"/>
@@ -4379,7 +4382,7 @@
         <v>17</v>
       </c>
       <c r="J58" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"050")</f>
         <v>050</v>
       </c>
       <c r="K58" s="4"/>
@@ -4428,7 +4431,7 @@
         <v>17</v>
       </c>
       <c r="J59" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"051")</f>
         <v>051</v>
       </c>
       <c r="K59" s="4"/>
@@ -4477,7 +4480,7 @@
         <v>17</v>
       </c>
       <c r="J60" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"052")</f>
         <v>052</v>
       </c>
       <c r="K60" s="4"/>
@@ -4526,7 +4529,7 @@
         <v>17</v>
       </c>
       <c r="J61" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="K61" s="4"/>
@@ -4575,7 +4578,7 @@
         <v>17</v>
       </c>
       <c r="J62" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"054")</f>
         <v>054</v>
       </c>
       <c r="K62" s="4"/>
@@ -4624,7 +4627,7 @@
         <v>17</v>
       </c>
       <c r="J63" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"055")</f>
         <v>055</v>
       </c>
       <c r="K63" s="4"/>
@@ -4673,7 +4676,7 @@
         <v>17</v>
       </c>
       <c r="J64" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"056")</f>
         <v>056</v>
       </c>
       <c r="K64" s="4"/>
@@ -4722,7 +4725,7 @@
         <v>17</v>
       </c>
       <c r="J65" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"057")</f>
         <v>057</v>
       </c>
       <c r="K65" s="4"/>
@@ -4771,7 +4774,7 @@
         <v>17</v>
       </c>
       <c r="J66" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"058")</f>
         <v>058</v>
       </c>
       <c r="K66" s="4"/>
@@ -4820,7 +4823,7 @@
         <v>17</v>
       </c>
       <c r="J67" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"059")</f>
         <v>059</v>
       </c>
       <c r="K67" s="4"/>
@@ -4869,7 +4872,7 @@
         <v>17</v>
       </c>
       <c r="J68" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"060")</f>
         <v>060</v>
       </c>
       <c r="K68" s="4"/>
@@ -4918,7 +4921,7 @@
         <v>17</v>
       </c>
       <c r="J69" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"061")</f>
         <v>061</v>
       </c>
       <c r="K69" s="4"/>
@@ -4967,7 +4970,7 @@
         <v>17</v>
       </c>
       <c r="J70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"062")</f>
         <v>062</v>
       </c>
       <c r="K70" s="4"/>
@@ -5016,7 +5019,7 @@
         <v>17</v>
       </c>
       <c r="J71" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"063")</f>
         <v>063</v>
       </c>
       <c r="K71" s="4"/>
@@ -5065,7 +5068,7 @@
         <v>17</v>
       </c>
       <c r="J72" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K72" s="4"/>
@@ -5114,7 +5117,7 @@
         <v>17</v>
       </c>
       <c r="J73" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K73" s="4"/>
@@ -5163,7 +5166,7 @@
         <v>17</v>
       </c>
       <c r="J74" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K74" s="4"/>
@@ -5212,7 +5215,7 @@
         <v>17</v>
       </c>
       <c r="J75" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K75" s="4"/>
@@ -5261,7 +5264,7 @@
         <v>17</v>
       </c>
       <c r="J76" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K76" s="4"/>
@@ -5310,7 +5313,7 @@
         <v>17</v>
       </c>
       <c r="J77" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"065")</f>
         <v>065</v>
       </c>
       <c r="K77" s="4"/>
@@ -5359,7 +5362,7 @@
         <v>17</v>
       </c>
       <c r="J78" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"066")</f>
         <v>066</v>
       </c>
       <c r="K78" s="4"/>
@@ -5408,7 +5411,7 @@
         <v>17</v>
       </c>
       <c r="J79" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"067")</f>
         <v>067</v>
       </c>
       <c r="K79" s="4"/>
@@ -5457,7 +5460,7 @@
         <v>17</v>
       </c>
       <c r="J80" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"068")</f>
         <v>068</v>
       </c>
       <c r="K80" s="4"/>
@@ -5506,7 +5509,7 @@
         <v>218</v>
       </c>
       <c r="J81" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"069")</f>
         <v>069</v>
       </c>
       <c r="K81" s="4"/>
@@ -5555,7 +5558,7 @@
         <v>218</v>
       </c>
       <c r="J82" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"070")</f>
         <v>070</v>
       </c>
       <c r="K82" s="4"/>
@@ -5604,7 +5607,7 @@
         <v>17</v>
       </c>
       <c r="J83" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"071")</f>
         <v>071</v>
       </c>
       <c r="K83" s="4"/>
@@ -5653,7 +5656,7 @@
         <v>17</v>
       </c>
       <c r="J84" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"072")</f>
         <v>072</v>
       </c>
       <c r="K84" s="4"/>
@@ -5702,7 +5705,7 @@
         <v>17</v>
       </c>
       <c r="J85" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"073")</f>
         <v>073</v>
       </c>
       <c r="K85" s="4"/>
@@ -5751,7 +5754,7 @@
         <v>17</v>
       </c>
       <c r="J86" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"074")</f>
         <v>074</v>
       </c>
       <c r="K86" s="4"/>
@@ -5800,7 +5803,7 @@
         <v>17</v>
       </c>
       <c r="J87" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K87" s="4"/>
@@ -5849,7 +5852,7 @@
         <v>17</v>
       </c>
       <c r="J88" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K88" s="4"/>
@@ -5898,7 +5901,7 @@
         <v>17</v>
       </c>
       <c r="J89" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"076")</f>
         <v>076</v>
       </c>
       <c r="K89" s="4"/>
@@ -5947,7 +5950,7 @@
         <v>17</v>
       </c>
       <c r="J90" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K90" s="4"/>
@@ -5996,7 +5999,7 @@
         <v>17</v>
       </c>
       <c r="J91" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K91" s="4"/>
@@ -6045,7 +6048,7 @@
         <v>17</v>
       </c>
       <c r="J92" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"078")</f>
         <v>078</v>
       </c>
       <c r="K92" s="4"/>
@@ -6094,7 +6097,7 @@
         <v>17</v>
       </c>
       <c r="J93" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"079")</f>
         <v>079</v>
       </c>
       <c r="K93" s="4"/>
@@ -6143,7 +6146,7 @@
         <v>17</v>
       </c>
       <c r="J94" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"080")</f>
         <v>080</v>
       </c>
       <c r="K94" s="4"/>
@@ -6192,7 +6195,7 @@
         <v>17</v>
       </c>
       <c r="J95" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"081")</f>
         <v>081</v>
       </c>
       <c r="K95" s="4"/>
@@ -6241,7 +6244,7 @@
         <v>17</v>
       </c>
       <c r="J96" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"082")</f>
         <v>082</v>
       </c>
       <c r="K96" s="4"/>
@@ -6290,7 +6293,7 @@
         <v>17</v>
       </c>
       <c r="J97" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"083")</f>
         <v>083</v>
       </c>
       <c r="K97" s="4"/>
@@ -6339,7 +6342,7 @@
         <v>268</v>
       </c>
       <c r="J98" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"084")</f>
         <v>084</v>
       </c>
       <c r="K98" s="4"/>
@@ -6388,7 +6391,7 @@
         <v>218</v>
       </c>
       <c r="J99" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"085")</f>
         <v>085</v>
       </c>
       <c r="K99" s="4"/>
@@ -6437,7 +6440,7 @@
         <v>218</v>
       </c>
       <c r="J100" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"086")</f>
         <v>086</v>
       </c>
       <c r="K100" s="4"/>
@@ -6486,7 +6489,7 @@
         <v>218</v>
       </c>
       <c r="J101" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"087")</f>
         <v>087</v>
       </c>
       <c r="K101" s="4"/>
@@ -6535,7 +6538,7 @@
         <v>218</v>
       </c>
       <c r="J102" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"088")</f>
         <v>088</v>
       </c>
       <c r="K102" s="4"/>
@@ -6584,7 +6587,7 @@
         <v>218</v>
       </c>
       <c r="J103" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"089")</f>
         <v>089</v>
       </c>
       <c r="K103" s="4"/>
@@ -6633,7 +6636,7 @@
         <v>218</v>
       </c>
       <c r="J104" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"090")</f>
         <v>090</v>
       </c>
       <c r="K104" s="4"/>
@@ -6682,7 +6685,7 @@
         <v>218</v>
       </c>
       <c r="J105" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"091")</f>
         <v>091</v>
       </c>
       <c r="K105" s="4"/>
@@ -6731,7 +6734,7 @@
         <v>17</v>
       </c>
       <c r="J106" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"092")</f>
         <v>092</v>
       </c>
       <c r="K106" s="4"/>
@@ -6780,7 +6783,7 @@
         <v>17</v>
       </c>
       <c r="J107" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"093")</f>
         <v>093</v>
       </c>
       <c r="K107" s="4"/>
@@ -6829,7 +6832,7 @@
         <v>17</v>
       </c>
       <c r="J108" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"094")</f>
         <v>094</v>
       </c>
       <c r="K108" s="4"/>
@@ -6878,7 +6881,7 @@
         <v>17</v>
       </c>
       <c r="J109" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"095")</f>
         <v>095</v>
       </c>
       <c r="K109" s="4"/>
@@ -6927,7 +6930,7 @@
         <v>17</v>
       </c>
       <c r="J110" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"096")</f>
         <v>096</v>
       </c>
       <c r="K110" s="4"/>
@@ -6976,7 +6979,7 @@
         <v>17</v>
       </c>
       <c r="J111" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"097")</f>
         <v>097</v>
       </c>
       <c r="K111" s="4"/>
@@ -7025,7 +7028,7 @@
         <v>17</v>
       </c>
       <c r="J112" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"098")</f>
         <v>098</v>
       </c>
       <c r="K112" s="4"/>
@@ -7074,7 +7077,7 @@
         <v>17</v>
       </c>
       <c r="J113" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"099")</f>
         <v>099</v>
       </c>
       <c r="K113" s="4"/>
@@ -7123,7 +7126,7 @@
         <v>17</v>
       </c>
       <c r="J114" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"100")</f>
         <v>100</v>
       </c>
       <c r="K114" s="4"/>
@@ -7172,7 +7175,7 @@
         <v>17</v>
       </c>
       <c r="J115" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"101")</f>
         <v>101</v>
       </c>
       <c r="K115" s="4"/>
@@ -7221,7 +7224,7 @@
         <v>17</v>
       </c>
       <c r="J116" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"102")</f>
         <v>102</v>
       </c>
       <c r="K116" s="4"/>
@@ -7270,7 +7273,7 @@
         <v>17</v>
       </c>
       <c r="J117" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"103")</f>
         <v>103</v>
       </c>
       <c r="K117" s="4"/>
@@ -7319,7 +7322,7 @@
         <v>218</v>
       </c>
       <c r="J118" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"104")</f>
         <v>104</v>
       </c>
       <c r="K118" s="4"/>
@@ -7368,7 +7371,7 @@
         <v>218</v>
       </c>
       <c r="J119" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"105")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"105")</f>
         <v>105</v>
       </c>
       <c r="K119" s="4"/>
@@ -7417,7 +7420,7 @@
         <v>218</v>
       </c>
       <c r="J120" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"106")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"106")</f>
         <v>106</v>
       </c>
       <c r="K120" s="4"/>
@@ -7466,7 +7469,7 @@
         <v>17</v>
       </c>
       <c r="J121" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"107")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"107")</f>
         <v>107</v>
       </c>
       <c r="K121" s="4"/>
@@ -7515,7 +7518,7 @@
         <v>17</v>
       </c>
       <c r="J122" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"108")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"108")</f>
         <v>108</v>
       </c>
       <c r="K122" s="4"/>
@@ -7564,7 +7567,7 @@
         <v>17</v>
       </c>
       <c r="J123" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"109")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"109")</f>
         <v>109</v>
       </c>
       <c r="K123" s="4"/>
@@ -7606,14 +7609,14 @@
       <c r="G124" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="H124" s="5" t="s">
+      <c r="H124" s="9" t="s">
         <v>328</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J124" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"110")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"110")</f>
         <v>110</v>
       </c>
       <c r="K124" s="4"/>
@@ -7662,7 +7665,7 @@
         <v>17</v>
       </c>
       <c r="J125" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"111")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"111")</f>
         <v>111</v>
       </c>
       <c r="K125" s="4"/>
@@ -7704,14 +7707,14 @@
       <c r="G126" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="H126" s="5" t="s">
+      <c r="H126" s="9" t="s">
         <v>332</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J126" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"112")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"112")</f>
         <v>112</v>
       </c>
       <c r="K126" s="4"/>
@@ -7760,7 +7763,7 @@
         <v>268</v>
       </c>
       <c r="J127" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"113")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"113")</f>
         <v>113</v>
       </c>
       <c r="K127" s="4"/>
@@ -7809,7 +7812,7 @@
         <v>268</v>
       </c>
       <c r="J128" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"114")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"114")</f>
         <v>114</v>
       </c>
       <c r="K128" s="4"/>
@@ -7858,7 +7861,7 @@
         <v>268</v>
       </c>
       <c r="J129" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"115")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"115")</f>
         <v>115</v>
       </c>
       <c r="K129" s="4"/>
@@ -7907,7 +7910,7 @@
         <v>268</v>
       </c>
       <c r="J130" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"116")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"116")</f>
         <v>116</v>
       </c>
       <c r="K130" s="4"/>
@@ -7947,16 +7950,16 @@
         <v>14</v>
       </c>
       <c r="G131" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H131" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="H131" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J131" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"117")</f>
         <v>117</v>
       </c>
       <c r="K131" s="4"/>
@@ -7978,34 +7981,34 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J132" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"118")</f>
         <v>118</v>
       </c>
       <c r="K132" s="4"/>
@@ -8027,35 +8030,35 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J133" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"119")</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <v>118</v>
       </c>
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
@@ -8076,35 +8079,35 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J134" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"120")</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
       </c>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
@@ -8125,35 +8128,35 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J135" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"121")</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
       </c>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
@@ -8174,19 +8177,19 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
@@ -8195,14 +8198,14 @@
         <v>355</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J136" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
-        <v>122</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
       </c>
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
@@ -8223,35 +8226,35 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H137" s="5" t="s">
         <v>357</v>
-      </c>
-      <c r="H137" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J137" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"122")</f>
-        <v>122</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <v>120</v>
       </c>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
@@ -8272,19 +8275,19 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
@@ -8299,8 +8302,8 @@
         <v>268</v>
       </c>
       <c r="J138" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"123")</f>
-        <v>123</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"121")</f>
+        <v>121</v>
       </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
@@ -8321,19 +8324,19 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
@@ -8342,14 +8345,14 @@
         <v>360</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J139" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
-        <v>124</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <v>120</v>
       </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
@@ -8370,35 +8373,35 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J140" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"124")</f>
-        <v>124</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <v>120</v>
       </c>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
@@ -8418,37 +8421,16 @@
       <c r="Z140" s="4"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="H141" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J141" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H141,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
-      </c>
+      <c r="A141" s="6"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
@@ -8467,37 +8449,16 @@
       <c r="Z141" s="4"/>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="H142" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="I142" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J142" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H142,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
-      </c>
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
@@ -8516,37 +8477,16 @@
       <c r="Z142" s="4"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="H143" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J143" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H143,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"125")</f>
-        <v>125</v>
-      </c>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
@@ -8565,37 +8505,15 @@
       <c r="Z143" s="4"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="H144" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J144" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H144,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
-      </c>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="6"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
@@ -8614,37 +8532,16 @@
       <c r="Z144" s="4"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="I145" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J145" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H145,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"127")</f>
-        <v>127</v>
-      </c>
+      <c r="A145" s="6"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="6"/>
+      <c r="H145" s="6"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
       <c r="K145" s="4"/>
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
@@ -8663,37 +8560,16 @@
       <c r="Z145" s="4"/>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="I146" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J146" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H146,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
-      </c>
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
@@ -8712,37 +8588,16 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="H147" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="I147" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J147" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H147,UNIQUE(FILTER($H$2:$H1076,$H$2:$H1076&lt;&gt;"""")),0),""000"")"),"126")</f>
-        <v>126</v>
-      </c>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
       <c r="K147" s="4"/>
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
@@ -8852,6 +8707,7 @@
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -9432,14 +9288,14 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
+      <c r="A172" s="10"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="10"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="10"/>
+      <c r="G172" s="10"/>
+      <c r="H172" s="10"/>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -9460,14 +9316,14 @@
       <c r="Z172" s="4"/>
     </row>
     <row r="173">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="10"/>
+      <c r="H173" s="10"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -9488,14 +9344,14 @@
       <c r="Z173" s="4"/>
     </row>
     <row r="174">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
+      <c r="A174" s="10"/>
+      <c r="B174" s="10"/>
+      <c r="C174" s="10"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="10"/>
+      <c r="G174" s="10"/>
+      <c r="H174" s="10"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -9516,14 +9372,14 @@
       <c r="Z174" s="4"/>
     </row>
     <row r="175">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
+      <c r="A175" s="10"/>
+      <c r="B175" s="10"/>
+      <c r="C175" s="10"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="10"/>
+      <c r="F175" s="10"/>
+      <c r="G175" s="10"/>
+      <c r="H175" s="10"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
@@ -9544,14 +9400,14 @@
       <c r="Z175" s="4"/>
     </row>
     <row r="176">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="10"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="10"/>
+      <c r="G176" s="10"/>
+      <c r="H176" s="10"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
@@ -9572,14 +9428,14 @@
       <c r="Z176" s="4"/>
     </row>
     <row r="177">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
+      <c r="A177" s="10"/>
+      <c r="B177" s="10"/>
+      <c r="C177" s="10"/>
+      <c r="D177" s="10"/>
+      <c r="E177" s="10"/>
+      <c r="F177" s="10"/>
+      <c r="G177" s="10"/>
+      <c r="H177" s="10"/>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
@@ -9600,14 +9456,14 @@
       <c r="Z177" s="4"/>
     </row>
     <row r="178">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
+      <c r="A178" s="10"/>
+      <c r="B178" s="10"/>
+      <c r="C178" s="10"/>
+      <c r="D178" s="10"/>
+      <c r="E178" s="10"/>
+      <c r="F178" s="10"/>
+      <c r="G178" s="10"/>
+      <c r="H178" s="10"/>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
@@ -9628,14 +9484,14 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179">
-      <c r="A179" s="9"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="10"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="10"/>
+      <c r="F179" s="10"/>
+      <c r="G179" s="10"/>
+      <c r="H179" s="10"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -9656,14 +9512,14 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180">
-      <c r="A180" s="9"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="10"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="10"/>
+      <c r="F180" s="10"/>
+      <c r="G180" s="10"/>
+      <c r="H180" s="10"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -9684,14 +9540,14 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181">
-      <c r="A181" s="9"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="10"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="10"/>
+      <c r="F181" s="10"/>
+      <c r="G181" s="10"/>
+      <c r="H181" s="10"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -9712,14 +9568,14 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182">
-      <c r="A182" s="9"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="10"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="10"/>
+      <c r="F182" s="10"/>
+      <c r="G182" s="10"/>
+      <c r="H182" s="10"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -9740,14 +9596,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="9"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="9"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="9"/>
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="10"/>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10"/>
+      <c r="G183" s="10"/>
+      <c r="H183" s="10"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -9768,14 +9624,14 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184">
-      <c r="A184" s="9"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="9"/>
+      <c r="A184" s="4"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="4"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -9796,14 +9652,14 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185">
-      <c r="A185" s="9"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="9"/>
+      <c r="A185" s="4"/>
+      <c r="B185" s="4"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -9824,14 +9680,14 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186">
-      <c r="A186" s="9"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
+      <c r="A186" s="4"/>
+      <c r="B186" s="4"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4"/>
+      <c r="G186" s="4"/>
+      <c r="H186" s="4"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -9852,14 +9708,14 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187">
-      <c r="A187" s="9"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="9"/>
+      <c r="A187" s="4"/>
+      <c r="B187" s="4"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
+      <c r="H187" s="4"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -9880,14 +9736,14 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188">
-      <c r="A188" s="9"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
+      <c r="A188" s="4"/>
+      <c r="B188" s="4"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -9908,14 +9764,14 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189">
-      <c r="A189" s="9"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -9936,14 +9792,14 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
+      <c r="A190" s="4"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -34575,202 +34431,6 @@
       <c r="Y1069" s="4"/>
       <c r="Z1069" s="4"/>
     </row>
-    <row r="1070">
-      <c r="A1070" s="4"/>
-      <c r="B1070" s="4"/>
-      <c r="C1070" s="4"/>
-      <c r="D1070" s="4"/>
-      <c r="E1070" s="4"/>
-      <c r="F1070" s="4"/>
-      <c r="G1070" s="4"/>
-      <c r="H1070" s="4"/>
-      <c r="I1070" s="4"/>
-      <c r="J1070" s="4"/>
-      <c r="K1070" s="4"/>
-      <c r="L1070" s="4"/>
-      <c r="M1070" s="4"/>
-      <c r="N1070" s="4"/>
-      <c r="O1070" s="4"/>
-      <c r="P1070" s="4"/>
-      <c r="Q1070" s="4"/>
-      <c r="R1070" s="4"/>
-      <c r="S1070" s="4"/>
-      <c r="T1070" s="4"/>
-      <c r="U1070" s="4"/>
-      <c r="V1070" s="4"/>
-      <c r="W1070" s="4"/>
-      <c r="X1070" s="4"/>
-      <c r="Y1070" s="4"/>
-      <c r="Z1070" s="4"/>
-    </row>
-    <row r="1071">
-      <c r="A1071" s="4"/>
-      <c r="B1071" s="4"/>
-      <c r="C1071" s="4"/>
-      <c r="D1071" s="4"/>
-      <c r="E1071" s="4"/>
-      <c r="F1071" s="4"/>
-      <c r="G1071" s="4"/>
-      <c r="H1071" s="4"/>
-      <c r="I1071" s="4"/>
-      <c r="J1071" s="4"/>
-      <c r="K1071" s="4"/>
-      <c r="L1071" s="4"/>
-      <c r="M1071" s="4"/>
-      <c r="N1071" s="4"/>
-      <c r="O1071" s="4"/>
-      <c r="P1071" s="4"/>
-      <c r="Q1071" s="4"/>
-      <c r="R1071" s="4"/>
-      <c r="S1071" s="4"/>
-      <c r="T1071" s="4"/>
-      <c r="U1071" s="4"/>
-      <c r="V1071" s="4"/>
-      <c r="W1071" s="4"/>
-      <c r="X1071" s="4"/>
-      <c r="Y1071" s="4"/>
-      <c r="Z1071" s="4"/>
-    </row>
-    <row r="1072">
-      <c r="A1072" s="4"/>
-      <c r="B1072" s="4"/>
-      <c r="C1072" s="4"/>
-      <c r="D1072" s="4"/>
-      <c r="E1072" s="4"/>
-      <c r="F1072" s="4"/>
-      <c r="G1072" s="4"/>
-      <c r="H1072" s="4"/>
-      <c r="I1072" s="4"/>
-      <c r="J1072" s="4"/>
-      <c r="K1072" s="4"/>
-      <c r="L1072" s="4"/>
-      <c r="M1072" s="4"/>
-      <c r="N1072" s="4"/>
-      <c r="O1072" s="4"/>
-      <c r="P1072" s="4"/>
-      <c r="Q1072" s="4"/>
-      <c r="R1072" s="4"/>
-      <c r="S1072" s="4"/>
-      <c r="T1072" s="4"/>
-      <c r="U1072" s="4"/>
-      <c r="V1072" s="4"/>
-      <c r="W1072" s="4"/>
-      <c r="X1072" s="4"/>
-      <c r="Y1072" s="4"/>
-      <c r="Z1072" s="4"/>
-    </row>
-    <row r="1073">
-      <c r="A1073" s="4"/>
-      <c r="B1073" s="4"/>
-      <c r="C1073" s="4"/>
-      <c r="D1073" s="4"/>
-      <c r="E1073" s="4"/>
-      <c r="F1073" s="4"/>
-      <c r="G1073" s="4"/>
-      <c r="H1073" s="4"/>
-      <c r="I1073" s="4"/>
-      <c r="J1073" s="4"/>
-      <c r="K1073" s="4"/>
-      <c r="L1073" s="4"/>
-      <c r="M1073" s="4"/>
-      <c r="N1073" s="4"/>
-      <c r="O1073" s="4"/>
-      <c r="P1073" s="4"/>
-      <c r="Q1073" s="4"/>
-      <c r="R1073" s="4"/>
-      <c r="S1073" s="4"/>
-      <c r="T1073" s="4"/>
-      <c r="U1073" s="4"/>
-      <c r="V1073" s="4"/>
-      <c r="W1073" s="4"/>
-      <c r="X1073" s="4"/>
-      <c r="Y1073" s="4"/>
-      <c r="Z1073" s="4"/>
-    </row>
-    <row r="1074">
-      <c r="A1074" s="4"/>
-      <c r="B1074" s="4"/>
-      <c r="C1074" s="4"/>
-      <c r="D1074" s="4"/>
-      <c r="E1074" s="4"/>
-      <c r="F1074" s="4"/>
-      <c r="G1074" s="4"/>
-      <c r="H1074" s="4"/>
-      <c r="I1074" s="4"/>
-      <c r="J1074" s="4"/>
-      <c r="K1074" s="4"/>
-      <c r="L1074" s="4"/>
-      <c r="M1074" s="4"/>
-      <c r="N1074" s="4"/>
-      <c r="O1074" s="4"/>
-      <c r="P1074" s="4"/>
-      <c r="Q1074" s="4"/>
-      <c r="R1074" s="4"/>
-      <c r="S1074" s="4"/>
-      <c r="T1074" s="4"/>
-      <c r="U1074" s="4"/>
-      <c r="V1074" s="4"/>
-      <c r="W1074" s="4"/>
-      <c r="X1074" s="4"/>
-      <c r="Y1074" s="4"/>
-      <c r="Z1074" s="4"/>
-    </row>
-    <row r="1075">
-      <c r="A1075" s="4"/>
-      <c r="B1075" s="4"/>
-      <c r="C1075" s="4"/>
-      <c r="D1075" s="4"/>
-      <c r="E1075" s="4"/>
-      <c r="F1075" s="4"/>
-      <c r="G1075" s="4"/>
-      <c r="H1075" s="4"/>
-      <c r="I1075" s="4"/>
-      <c r="J1075" s="4"/>
-      <c r="K1075" s="4"/>
-      <c r="L1075" s="4"/>
-      <c r="M1075" s="4"/>
-      <c r="N1075" s="4"/>
-      <c r="O1075" s="4"/>
-      <c r="P1075" s="4"/>
-      <c r="Q1075" s="4"/>
-      <c r="R1075" s="4"/>
-      <c r="S1075" s="4"/>
-      <c r="T1075" s="4"/>
-      <c r="U1075" s="4"/>
-      <c r="V1075" s="4"/>
-      <c r="W1075" s="4"/>
-      <c r="X1075" s="4"/>
-      <c r="Y1075" s="4"/>
-      <c r="Z1075" s="4"/>
-    </row>
-    <row r="1076">
-      <c r="A1076" s="4"/>
-      <c r="B1076" s="4"/>
-      <c r="C1076" s="4"/>
-      <c r="D1076" s="4"/>
-      <c r="E1076" s="4"/>
-      <c r="F1076" s="4"/>
-      <c r="G1076" s="4"/>
-      <c r="H1076" s="4"/>
-      <c r="I1076" s="4"/>
-      <c r="J1076" s="4"/>
-      <c r="K1076" s="4"/>
-      <c r="L1076" s="4"/>
-      <c r="M1076" s="4"/>
-      <c r="N1076" s="4"/>
-      <c r="O1076" s="4"/>
-      <c r="P1076" s="4"/>
-      <c r="Q1076" s="4"/>
-      <c r="R1076" s="4"/>
-      <c r="S1076" s="4"/>
-      <c r="T1076" s="4"/>
-      <c r="U1076" s="4"/>
-      <c r="V1076" s="4"/>
-      <c r="W1076" s="4"/>
-      <c r="X1076" s="4"/>
-      <c r="Y1076" s="4"/>
-      <c r="Z1076" s="4"/>
-    </row>
   </sheetData>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>

--- a/Catálogo ROP-LOP 2027.xlsx
+++ b/Catálogo ROP-LOP 2027.xlsx
@@ -13,17 +13,62 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={04545d8b-8847-49cf-8bac-f4dfbabfeb4a}</author>
-    <author>tc={14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}</author>
-    <author>tc={84478949-6a9b-4a11-a54e-89080d944ab9}</author>
-    <author>tc={8f6204b8-4fa0-4319-9ed2-65baaaad30d6}</author>
-    <author>tc={b513cf22-f97e-4149-befb-1089378921cd}</author>
-    <author>tc={bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}</author>
-    <author>tc={d81b8a74-c48a-4dea-86a7-de993678a0f8}</author>
-    <author>tc={eb8ff5e1-0a62-4485-8ff7-247a481aae65}</author>
+    <author>tc={3831e309-e861-4d46-949f-66bb0476ad49}</author>
+    <author>tc={6d6ac059-2989-4293-be0e-0a709fc7f7c6}</author>
+    <author>tc={893e736e-ac4f-433e-b2de-297ecf7b3a6c}</author>
+    <author>tc={9e644b7b-7e8f-45e1-ba7b-1f0ab862800a}</author>
+    <author>tc={bef264f3-007a-4f69-a2c7-d91c70f6ad6a}</author>
+    <author>tc={d286386c-ece4-4deb-8624-51a8525a0217}</author>
+    <author>tc={e4325d8e-c784-4f13-b8ed-1a9b655eba57}</author>
+    <author>tc={feb3938d-12a7-445c-8ca5-4b004bde5e59}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{04545d8b-8847-49cf-8bac-f4dfbabfeb4a}" ref="F89">
+    <comment authorId="0" xr:uid="{3831e309-e861-4d46-949f-66bb0476ad49}" ref="H41">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{6d6ac059-2989-4293-be0e-0a709fc7f7c6}" ref="H126">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Solo tiene recurso propio
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{893e736e-ac4f-433e-b2de-297ecf7b3a6c}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{9e644b7b-7e8f-45e1-ba7b-1f0ab862800a}" ref="H124">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Tiene recurso propio
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{bef264f3-007a-4f69-a2c7-d91c70f6ad6a}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Le cambiaron la transversalidad
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{d286386c-ece4-4deb-8624-51a8525a0217}" ref="F89">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,7 +77,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}" ref="F18">
+    <comment authorId="6" xr:uid="{e4325d8e-c784-4f13-b8ed-1a9b655eba57}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -41,34 +86,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{84478949-6a9b-4a11-a54e-89080d944ab9}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	De momento se registra el nombre del componente; a la espera de nombre de la ROP.
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{8f6204b8-4fa0-4319-9ed2-65baaaad30d6}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Le cambiaron la transversalidad
-</t>
-      </text>
-    </comment>
-    <comment authorId="4" xr:uid="{b513cf22-f97e-4149-befb-1089378921cd}" ref="H124">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Tiene recurso propio
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}" ref="F18">
+    <comment authorId="7" xr:uid="{feb3938d-12a7-445c-8ca5-4b004bde5e59}" ref="F18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -77,30 +95,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="6" xr:uid="{d81b8a74-c48a-4dea-86a7-de993678a0f8}" ref="H41">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{eb8ff5e1-0a62-4485-8ff7-247a481aae65}" ref="H126">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Solo tiene recurso propio
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="361">
   <si>
     <t>UP</t>
   </si>
@@ -1134,9 +1134,6 @@
   </si>
   <si>
     <t xml:space="preserve">Programa Ayuda Económica para las y los Estudiantes de la Escuela Normal Rural Miguel Hidalgo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayuda económica para las y los estudiantes del Programa Talento la Estilo Jalisco </t>
   </si>
   <si>
     <t>14</t>
@@ -1313,10 +1310,10 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" providerId="google-sheets"/>
-  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{28e245ef-59ec-4ecf-9243-55a9814940ff}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{46d3832a-6c5c-499e-b76f-e71956d7f64e}" providerId="google-sheets"/>
-  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" providerId="google-sheets"/>
+  <x18tc:person displayName="Karla Marcela Padilla Chávez" id="{0568ce2a-6e52-40df-b7b7-b6e48729d2e8}" providerId="google-sheets"/>
+  <x18tc:person displayName="Guillermo Amezcua Moreno" id="{52c195d9-4250-4cdc-8eeb-3f91aa8a60e0}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mariana Claret Gutiérrez Márquez" id="{0d2446df-4c3a-4c8d-a5d2-3b8fe4542772}" providerId="google-sheets"/>
+  <x18tc:person displayName="Armando Yair Cárdenas Ávila" id="{7b76393a-e314-479a-a669-74d34632ac9b}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1516,28 +1513,28 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{28e245ef-59ec-4ecf-9243-55a9814940ff}" id="{d81b8a74-c48a-4dea-86a7-de993678a0f8}" done="0">
+  <x18tc:threadedComment ref="H41" dT="2026-07-06T19:48:27.00" personId="{52c195d9-4250-4cdc-8eeb-3f91aa8a60e0}" id="{3831e309-e861-4d46-949f-66bb0476ad49}" done="0">
     <x18tc:text xml:space="preserve">A la espera de confirmación del nombre de la ROP, sin embargo ese es el tema de la intervención.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H126" dT="2026-08-12T23:13:36.00" personId="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" id="{eb8ff5e1-0a62-4485-8ff7-247a481aae65}" done="0">
+  <x18tc:threadedComment ref="H126" dT="2026-08-12T23:13:36.00" personId="{7b76393a-e314-479a-a669-74d34632ac9b}" id="{6d6ac059-2989-4293-be0e-0a709fc7f7c6}" done="0">
     <x18tc:text xml:space="preserve">Solo tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{04545d8b-8847-49cf-8bac-f4dfbabfeb4a}" done="0">
+  <x18tc:threadedComment ref="F89" dT="2026-06-25T21:11:19.00" personId="{0568ce2a-6e52-40df-b7b7-b6e48729d2e8}" id="{d286386c-ece4-4deb-8624-51a8525a0217}" done="0">
     <x18tc:text xml:space="preserve">Actalmente es un Lineamiento de Operación</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{28e245ef-59ec-4ecf-9243-55a9814940ff}" id="{84478949-6a9b-4a11-a54e-89080d944ab9}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-06T19:50:38.00" personId="{52c195d9-4250-4cdc-8eeb-3f91aa8a60e0}" id="{893e736e-ac4f-433e-b2de-297ecf7b3a6c}" done="0">
     <x18tc:text xml:space="preserve">De momento se registra el nombre del componente; a la espera de nombre de la ROP.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H124" dT="2026-08-12T23:13:08.00" personId="{4f5c7248-ae10-42f9-bb3d-e0326d7a4f37}" id="{b513cf22-f97e-4149-befb-1089378921cd}" done="0">
+  <x18tc:threadedComment ref="H124" dT="2026-08-12T23:13:08.00" personId="{7b76393a-e314-479a-a669-74d34632ac9b}" id="{9e644b7b-7e8f-45e1-ba7b-1f0ab862800a}" done="0">
     <x18tc:text xml:space="preserve">Tiene recurso propio</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{46d3832a-6c5c-499e-b76f-e71956d7f64e}" id="{8f6204b8-4fa0-4319-9ed2-65baaaad30d6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-08-03T23:05:51.00" personId="{0d2446df-4c3a-4c8d-a5d2-3b8fe4542772}" id="{bef264f3-007a-4f69-a2c7-d91c70f6ad6a}" done="0">
     <x18tc:text xml:space="preserve">Le cambiaron la transversalidad</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{14ac1a6e-f3c5-47f3-bc23-85c2c006a86c}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:15:11.00" personId="{0568ce2a-6e52-40df-b7b7-b6e48729d2e8}" id="{e4325d8e-c784-4f13-b8ed-1a9b655eba57}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con clasificación Programpatica  E</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{bc8e0f63-7ab0-46ea-ae60-2d98e7c40161}" id="{bd7f1d42-aec2-44bb-bdaf-c87c177b7c50}" done="1">
+  <x18tc:threadedComment ref="F18" dT="2026-06-25T21:43:13.00" personId="{0568ce2a-6e52-40df-b7b7-b6e48729d2e8}" id="{feb3938d-12a7-445c-8ca5-4b004bde5e59}" done="1">
     <x18tc:text xml:space="preserve">Actualmente cuenta con una clasificación programática con letra E</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1638,7 +1635,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H2,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K2" s="4"/>
@@ -1687,7 +1684,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H3,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K3" s="4"/>
@@ -1736,7 +1733,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H4,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K4" s="4"/>
@@ -1785,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"002")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H5,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"002")</f>
         <v>002</v>
       </c>
       <c r="K5" s="4"/>
@@ -1834,7 +1831,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"003")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H6,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"003")</f>
         <v>003</v>
       </c>
       <c r="K6" s="4"/>
@@ -1883,7 +1880,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"001")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H7,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"001")</f>
         <v>001</v>
       </c>
       <c r="K7" s="4"/>
@@ -1932,7 +1929,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"004")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H8,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"004")</f>
         <v>004</v>
       </c>
       <c r="K8" s="4"/>
@@ -1981,7 +1978,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"005")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H9,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"005")</f>
         <v>005</v>
       </c>
       <c r="K9" s="4"/>
@@ -2030,7 +2027,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"006")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H10,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"006")</f>
         <v>006</v>
       </c>
       <c r="K10" s="4"/>
@@ -2079,7 +2076,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"007")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H11,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"007")</f>
         <v>007</v>
       </c>
       <c r="K11" s="4"/>
@@ -2128,7 +2125,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"008")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H12,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"008")</f>
         <v>008</v>
       </c>
       <c r="K12" s="4"/>
@@ -2177,7 +2174,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"009")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H13,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"009")</f>
         <v>009</v>
       </c>
       <c r="K13" s="4"/>
@@ -2226,7 +2223,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"010")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H14,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"010")</f>
         <v>010</v>
       </c>
       <c r="K14" s="4"/>
@@ -2275,7 +2272,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"011")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H15,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"011")</f>
         <v>011</v>
       </c>
       <c r="K15" s="4"/>
@@ -2324,7 +2321,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"012")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H16,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"012")</f>
         <v>012</v>
       </c>
       <c r="K16" s="4"/>
@@ -2373,7 +2370,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"013")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H17,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"013")</f>
         <v>013</v>
       </c>
       <c r="K17" s="4"/>
@@ -2422,7 +2419,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"014")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H18,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"014")</f>
         <v>014</v>
       </c>
       <c r="K18" s="4"/>
@@ -2471,7 +2468,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"015")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H19,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"015")</f>
         <v>015</v>
       </c>
       <c r="K19" s="4"/>
@@ -2520,7 +2517,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"016")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H20,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"016")</f>
         <v>016</v>
       </c>
       <c r="K20" s="4"/>
@@ -2569,7 +2566,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"017")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H21,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"017")</f>
         <v>017</v>
       </c>
       <c r="K21" s="4"/>
@@ -2618,7 +2615,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"018")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H22,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"018")</f>
         <v>018</v>
       </c>
       <c r="K22" s="4"/>
@@ -2667,7 +2664,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"019")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H23,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"019")</f>
         <v>019</v>
       </c>
       <c r="K23" s="4"/>
@@ -2716,7 +2713,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"020")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H24,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"020")</f>
         <v>020</v>
       </c>
       <c r="K24" s="4"/>
@@ -2765,7 +2762,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"021")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H25,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"021")</f>
         <v>021</v>
       </c>
       <c r="K25" s="4"/>
@@ -2814,7 +2811,7 @@
         <v>17</v>
       </c>
       <c r="J26" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"022")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H26,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"022")</f>
         <v>022</v>
       </c>
       <c r="K26" s="4"/>
@@ -2863,7 +2860,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"023")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H27,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"023")</f>
         <v>023</v>
       </c>
       <c r="K27" s="4"/>
@@ -2912,7 +2909,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"024")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H28,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"024")</f>
         <v>024</v>
       </c>
       <c r="K28" s="4"/>
@@ -2961,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"025")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H29,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"025")</f>
         <v>025</v>
       </c>
       <c r="K29" s="4"/>
@@ -3010,7 +3007,7 @@
         <v>17</v>
       </c>
       <c r="J30" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"026")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H30,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"026")</f>
         <v>026</v>
       </c>
       <c r="K30" s="4"/>
@@ -3059,7 +3056,7 @@
         <v>17</v>
       </c>
       <c r="J31" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"027")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H31,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"027")</f>
         <v>027</v>
       </c>
       <c r="K31" s="4"/>
@@ -3108,7 +3105,7 @@
         <v>17</v>
       </c>
       <c r="J32" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"028")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H32,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"028")</f>
         <v>028</v>
       </c>
       <c r="K32" s="4"/>
@@ -3157,7 +3154,7 @@
         <v>17</v>
       </c>
       <c r="J33" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"029")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H33,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"029")</f>
         <v>029</v>
       </c>
       <c r="K33" s="4"/>
@@ -3206,7 +3203,7 @@
         <v>17</v>
       </c>
       <c r="J34" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"030")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H34,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"030")</f>
         <v>030</v>
       </c>
       <c r="K34" s="4"/>
@@ -3255,7 +3252,7 @@
         <v>17</v>
       </c>
       <c r="J35" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H35,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K35" s="4"/>
@@ -3304,7 +3301,7 @@
         <v>17</v>
       </c>
       <c r="J36" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"031")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H36,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"031")</f>
         <v>031</v>
       </c>
       <c r="K36" s="4"/>
@@ -3353,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="J37" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"032")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H37,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"032")</f>
         <v>032</v>
       </c>
       <c r="K37" s="4"/>
@@ -3402,7 +3399,7 @@
         <v>17</v>
       </c>
       <c r="J38" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H38,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K38" s="4"/>
@@ -3451,7 +3448,7 @@
         <v>112</v>
       </c>
       <c r="J39" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"033")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H39,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"033")</f>
         <v>033</v>
       </c>
       <c r="K39" s="4"/>
@@ -3500,7 +3497,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"034")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H40,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"034")</f>
         <v>034</v>
       </c>
       <c r="K40" s="4"/>
@@ -3549,7 +3546,7 @@
         <v>17</v>
       </c>
       <c r="J41" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"035")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H41,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"035")</f>
         <v>035</v>
       </c>
       <c r="K41" s="4"/>
@@ -3598,7 +3595,7 @@
         <v>17</v>
       </c>
       <c r="J42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"036")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H42,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"036")</f>
         <v>036</v>
       </c>
       <c r="K42" s="4"/>
@@ -3647,7 +3644,7 @@
         <v>17</v>
       </c>
       <c r="J43" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H43,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K43" s="4"/>
@@ -3696,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H44,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K44" s="4"/>
@@ -3745,7 +3742,7 @@
         <v>17</v>
       </c>
       <c r="J45" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"037")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H45,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"037")</f>
         <v>037</v>
       </c>
       <c r="K45" s="4"/>
@@ -3794,7 +3791,7 @@
         <v>17</v>
       </c>
       <c r="J46" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"038")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H46,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"038")</f>
         <v>038</v>
       </c>
       <c r="K46" s="4"/>
@@ -3843,7 +3840,7 @@
         <v>17</v>
       </c>
       <c r="J47" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"039")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H47,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"039")</f>
         <v>039</v>
       </c>
       <c r="K47" s="4"/>
@@ -3892,7 +3889,7 @@
         <v>17</v>
       </c>
       <c r="J48" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"040")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H48,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"040")</f>
         <v>040</v>
       </c>
       <c r="K48" s="4"/>
@@ -3941,7 +3938,7 @@
         <v>17</v>
       </c>
       <c r="J49" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"041")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H49,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"041")</f>
         <v>041</v>
       </c>
       <c r="K49" s="4"/>
@@ -3990,7 +3987,7 @@
         <v>17</v>
       </c>
       <c r="J50" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"042")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H50,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"042")</f>
         <v>042</v>
       </c>
       <c r="K50" s="4"/>
@@ -4039,7 +4036,7 @@
         <v>17</v>
       </c>
       <c r="J51" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"043")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H51,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"043")</f>
         <v>043</v>
       </c>
       <c r="K51" s="4"/>
@@ -4088,7 +4085,7 @@
         <v>17</v>
       </c>
       <c r="J52" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"044")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H52,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"044")</f>
         <v>044</v>
       </c>
       <c r="K52" s="4"/>
@@ -4137,7 +4134,7 @@
         <v>17</v>
       </c>
       <c r="J53" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"045")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H53,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"045")</f>
         <v>045</v>
       </c>
       <c r="K53" s="4"/>
@@ -4186,7 +4183,7 @@
         <v>17</v>
       </c>
       <c r="J54" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"046")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H54,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"046")</f>
         <v>046</v>
       </c>
       <c r="K54" s="4"/>
@@ -4235,7 +4232,7 @@
         <v>17</v>
       </c>
       <c r="J55" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"047")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H55,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"047")</f>
         <v>047</v>
       </c>
       <c r="K55" s="4"/>
@@ -4284,7 +4281,7 @@
         <v>17</v>
       </c>
       <c r="J56" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"048")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H56,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"048")</f>
         <v>048</v>
       </c>
       <c r="K56" s="4"/>
@@ -4333,7 +4330,7 @@
         <v>17</v>
       </c>
       <c r="J57" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"049")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H57,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"049")</f>
         <v>049</v>
       </c>
       <c r="K57" s="4"/>
@@ -4382,7 +4379,7 @@
         <v>17</v>
       </c>
       <c r="J58" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"050")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H58,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"050")</f>
         <v>050</v>
       </c>
       <c r="K58" s="4"/>
@@ -4431,7 +4428,7 @@
         <v>17</v>
       </c>
       <c r="J59" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"051")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H59,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"051")</f>
         <v>051</v>
       </c>
       <c r="K59" s="4"/>
@@ -4480,7 +4477,7 @@
         <v>17</v>
       </c>
       <c r="J60" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"052")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H60,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"052")</f>
         <v>052</v>
       </c>
       <c r="K60" s="4"/>
@@ -4529,7 +4526,7 @@
         <v>17</v>
       </c>
       <c r="J61" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"053")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H61,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"053")</f>
         <v>053</v>
       </c>
       <c r="K61" s="4"/>
@@ -4578,7 +4575,7 @@
         <v>17</v>
       </c>
       <c r="J62" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"054")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H62,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"054")</f>
         <v>054</v>
       </c>
       <c r="K62" s="4"/>
@@ -4627,7 +4624,7 @@
         <v>17</v>
       </c>
       <c r="J63" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"055")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H63,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"055")</f>
         <v>055</v>
       </c>
       <c r="K63" s="4"/>
@@ -4676,7 +4673,7 @@
         <v>17</v>
       </c>
       <c r="J64" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"056")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H64,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"056")</f>
         <v>056</v>
       </c>
       <c r="K64" s="4"/>
@@ -4725,7 +4722,7 @@
         <v>17</v>
       </c>
       <c r="J65" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"057")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H65,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"057")</f>
         <v>057</v>
       </c>
       <c r="K65" s="4"/>
@@ -4774,7 +4771,7 @@
         <v>17</v>
       </c>
       <c r="J66" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"058")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H66,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"058")</f>
         <v>058</v>
       </c>
       <c r="K66" s="4"/>
@@ -4823,7 +4820,7 @@
         <v>17</v>
       </c>
       <c r="J67" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"059")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H67,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"059")</f>
         <v>059</v>
       </c>
       <c r="K67" s="4"/>
@@ -4872,7 +4869,7 @@
         <v>17</v>
       </c>
       <c r="J68" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"060")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H68,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"060")</f>
         <v>060</v>
       </c>
       <c r="K68" s="4"/>
@@ -4921,7 +4918,7 @@
         <v>17</v>
       </c>
       <c r="J69" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"061")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H69,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"061")</f>
         <v>061</v>
       </c>
       <c r="K69" s="4"/>
@@ -4970,7 +4967,7 @@
         <v>17</v>
       </c>
       <c r="J70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"062")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H70,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"062")</f>
         <v>062</v>
       </c>
       <c r="K70" s="4"/>
@@ -5019,7 +5016,7 @@
         <v>17</v>
       </c>
       <c r="J71" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"063")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H71,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"063")</f>
         <v>063</v>
       </c>
       <c r="K71" s="4"/>
@@ -5068,7 +5065,7 @@
         <v>17</v>
       </c>
       <c r="J72" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H72,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K72" s="4"/>
@@ -5117,7 +5114,7 @@
         <v>17</v>
       </c>
       <c r="J73" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H73,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K73" s="4"/>
@@ -5166,7 +5163,7 @@
         <v>17</v>
       </c>
       <c r="J74" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H74,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K74" s="4"/>
@@ -5215,7 +5212,7 @@
         <v>17</v>
       </c>
       <c r="J75" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H75,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K75" s="4"/>
@@ -5264,7 +5261,7 @@
         <v>17</v>
       </c>
       <c r="J76" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"064")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H76,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"064")</f>
         <v>064</v>
       </c>
       <c r="K76" s="4"/>
@@ -5313,7 +5310,7 @@
         <v>17</v>
       </c>
       <c r="J77" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"065")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H77,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"065")</f>
         <v>065</v>
       </c>
       <c r="K77" s="4"/>
@@ -5362,7 +5359,7 @@
         <v>17</v>
       </c>
       <c r="J78" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"066")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H78,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"066")</f>
         <v>066</v>
       </c>
       <c r="K78" s="4"/>
@@ -5411,7 +5408,7 @@
         <v>17</v>
       </c>
       <c r="J79" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"067")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H79,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"067")</f>
         <v>067</v>
       </c>
       <c r="K79" s="4"/>
@@ -5460,7 +5457,7 @@
         <v>17</v>
       </c>
       <c r="J80" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"068")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H80,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"068")</f>
         <v>068</v>
       </c>
       <c r="K80" s="4"/>
@@ -5509,7 +5506,7 @@
         <v>218</v>
       </c>
       <c r="J81" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"069")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H81,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"069")</f>
         <v>069</v>
       </c>
       <c r="K81" s="4"/>
@@ -5558,7 +5555,7 @@
         <v>218</v>
       </c>
       <c r="J82" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"070")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H82,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"070")</f>
         <v>070</v>
       </c>
       <c r="K82" s="4"/>
@@ -5607,7 +5604,7 @@
         <v>17</v>
       </c>
       <c r="J83" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"071")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H83,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"071")</f>
         <v>071</v>
       </c>
       <c r="K83" s="4"/>
@@ -5656,7 +5653,7 @@
         <v>17</v>
       </c>
       <c r="J84" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"072")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H84,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"072")</f>
         <v>072</v>
       </c>
       <c r="K84" s="4"/>
@@ -5705,7 +5702,7 @@
         <v>17</v>
       </c>
       <c r="J85" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"073")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H85,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"073")</f>
         <v>073</v>
       </c>
       <c r="K85" s="4"/>
@@ -5754,7 +5751,7 @@
         <v>17</v>
       </c>
       <c r="J86" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"074")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H86,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"074")</f>
         <v>074</v>
       </c>
       <c r="K86" s="4"/>
@@ -5803,7 +5800,7 @@
         <v>17</v>
       </c>
       <c r="J87" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H87,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K87" s="4"/>
@@ -5852,7 +5849,7 @@
         <v>17</v>
       </c>
       <c r="J88" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"075")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H88,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"075")</f>
         <v>075</v>
       </c>
       <c r="K88" s="4"/>
@@ -5901,7 +5898,7 @@
         <v>17</v>
       </c>
       <c r="J89" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"076")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H89,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"076")</f>
         <v>076</v>
       </c>
       <c r="K89" s="4"/>
@@ -5950,7 +5947,7 @@
         <v>17</v>
       </c>
       <c r="J90" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H90,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K90" s="4"/>
@@ -5999,7 +5996,7 @@
         <v>17</v>
       </c>
       <c r="J91" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"077")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H91,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"077")</f>
         <v>077</v>
       </c>
       <c r="K91" s="4"/>
@@ -6048,7 +6045,7 @@
         <v>17</v>
       </c>
       <c r="J92" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"078")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H92,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"078")</f>
         <v>078</v>
       </c>
       <c r="K92" s="4"/>
@@ -6097,7 +6094,7 @@
         <v>17</v>
       </c>
       <c r="J93" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"079")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H93,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"079")</f>
         <v>079</v>
       </c>
       <c r="K93" s="4"/>
@@ -6146,7 +6143,7 @@
         <v>17</v>
       </c>
       <c r="J94" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"080")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H94,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"080")</f>
         <v>080</v>
       </c>
       <c r="K94" s="4"/>
@@ -6195,7 +6192,7 @@
         <v>17</v>
       </c>
       <c r="J95" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"081")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H95,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"081")</f>
         <v>081</v>
       </c>
       <c r="K95" s="4"/>
@@ -6244,7 +6241,7 @@
         <v>17</v>
       </c>
       <c r="J96" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"082")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H96,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"082")</f>
         <v>082</v>
       </c>
       <c r="K96" s="4"/>
@@ -6293,7 +6290,7 @@
         <v>17</v>
       </c>
       <c r="J97" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"083")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H97,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"083")</f>
         <v>083</v>
       </c>
       <c r="K97" s="4"/>
@@ -6342,7 +6339,7 @@
         <v>268</v>
       </c>
       <c r="J98" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"084")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H98,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"084")</f>
         <v>084</v>
       </c>
       <c r="K98" s="4"/>
@@ -6391,7 +6388,7 @@
         <v>218</v>
       </c>
       <c r="J99" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"085")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H99,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"085")</f>
         <v>085</v>
       </c>
       <c r="K99" s="4"/>
@@ -6440,7 +6437,7 @@
         <v>218</v>
       </c>
       <c r="J100" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"086")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H100,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"086")</f>
         <v>086</v>
       </c>
       <c r="K100" s="4"/>
@@ -6489,7 +6486,7 @@
         <v>218</v>
       </c>
       <c r="J101" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"087")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H101,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"087")</f>
         <v>087</v>
       </c>
       <c r="K101" s="4"/>
@@ -6538,7 +6535,7 @@
         <v>218</v>
       </c>
       <c r="J102" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"088")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H102,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"088")</f>
         <v>088</v>
       </c>
       <c r="K102" s="4"/>
@@ -6587,7 +6584,7 @@
         <v>218</v>
       </c>
       <c r="J103" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"089")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H103,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"089")</f>
         <v>089</v>
       </c>
       <c r="K103" s="4"/>
@@ -6636,7 +6633,7 @@
         <v>218</v>
       </c>
       <c r="J104" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"090")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H104,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"090")</f>
         <v>090</v>
       </c>
       <c r="K104" s="4"/>
@@ -6685,7 +6682,7 @@
         <v>218</v>
       </c>
       <c r="J105" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"091")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H105,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"091")</f>
         <v>091</v>
       </c>
       <c r="K105" s="4"/>
@@ -6734,7 +6731,7 @@
         <v>17</v>
       </c>
       <c r="J106" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"092")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H106,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"092")</f>
         <v>092</v>
       </c>
       <c r="K106" s="4"/>
@@ -6783,7 +6780,7 @@
         <v>17</v>
       </c>
       <c r="J107" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"093")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H107,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"093")</f>
         <v>093</v>
       </c>
       <c r="K107" s="4"/>
@@ -6832,7 +6829,7 @@
         <v>17</v>
       </c>
       <c r="J108" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"094")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H108,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"094")</f>
         <v>094</v>
       </c>
       <c r="K108" s="4"/>
@@ -6881,7 +6878,7 @@
         <v>17</v>
       </c>
       <c r="J109" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"095")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H109,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"095")</f>
         <v>095</v>
       </c>
       <c r="K109" s="4"/>
@@ -6930,7 +6927,7 @@
         <v>17</v>
       </c>
       <c r="J110" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"096")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H110,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"096")</f>
         <v>096</v>
       </c>
       <c r="K110" s="4"/>
@@ -6979,7 +6976,7 @@
         <v>17</v>
       </c>
       <c r="J111" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"097")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H111,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"097")</f>
         <v>097</v>
       </c>
       <c r="K111" s="4"/>
@@ -7028,7 +7025,7 @@
         <v>17</v>
       </c>
       <c r="J112" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"098")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H112,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"098")</f>
         <v>098</v>
       </c>
       <c r="K112" s="4"/>
@@ -7077,7 +7074,7 @@
         <v>17</v>
       </c>
       <c r="J113" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"099")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H113,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"099")</f>
         <v>099</v>
       </c>
       <c r="K113" s="4"/>
@@ -7126,7 +7123,7 @@
         <v>17</v>
       </c>
       <c r="J114" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"100")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H114,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"100")</f>
         <v>100</v>
       </c>
       <c r="K114" s="4"/>
@@ -7175,7 +7172,7 @@
         <v>17</v>
       </c>
       <c r="J115" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"101")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H115,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"101")</f>
         <v>101</v>
       </c>
       <c r="K115" s="4"/>
@@ -7224,7 +7221,7 @@
         <v>17</v>
       </c>
       <c r="J116" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"102")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H116,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"102")</f>
         <v>102</v>
       </c>
       <c r="K116" s="4"/>
@@ -7273,7 +7270,7 @@
         <v>17</v>
       </c>
       <c r="J117" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"103")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H117,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"103")</f>
         <v>103</v>
       </c>
       <c r="K117" s="4"/>
@@ -7322,7 +7319,7 @@
         <v>218</v>
       </c>
       <c r="J118" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"104")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H118,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"104")</f>
         <v>104</v>
       </c>
       <c r="K118" s="4"/>
@@ -7371,7 +7368,7 @@
         <v>218</v>
       </c>
       <c r="J119" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"105")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H119,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"105")</f>
         <v>105</v>
       </c>
       <c r="K119" s="4"/>
@@ -7420,7 +7417,7 @@
         <v>218</v>
       </c>
       <c r="J120" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"106")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H120,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"106")</f>
         <v>106</v>
       </c>
       <c r="K120" s="4"/>
@@ -7469,7 +7466,7 @@
         <v>17</v>
       </c>
       <c r="J121" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"107")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H121,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"107")</f>
         <v>107</v>
       </c>
       <c r="K121" s="4"/>
@@ -7518,7 +7515,7 @@
         <v>17</v>
       </c>
       <c r="J122" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"108")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H122,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"108")</f>
         <v>108</v>
       </c>
       <c r="K122" s="4"/>
@@ -7567,7 +7564,7 @@
         <v>17</v>
       </c>
       <c r="J123" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"109")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H123,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"109")</f>
         <v>109</v>
       </c>
       <c r="K123" s="4"/>
@@ -7616,7 +7613,7 @@
         <v>17</v>
       </c>
       <c r="J124" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"110")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H124,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"110")</f>
         <v>110</v>
       </c>
       <c r="K124" s="4"/>
@@ -7665,7 +7662,7 @@
         <v>17</v>
       </c>
       <c r="J125" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"111")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H125,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"111")</f>
         <v>111</v>
       </c>
       <c r="K125" s="4"/>
@@ -7714,7 +7711,7 @@
         <v>17</v>
       </c>
       <c r="J126" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"112")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H126,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"112")</f>
         <v>112</v>
       </c>
       <c r="K126" s="4"/>
@@ -7763,7 +7760,7 @@
         <v>268</v>
       </c>
       <c r="J127" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"113")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H127,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"113")</f>
         <v>113</v>
       </c>
       <c r="K127" s="4"/>
@@ -7812,7 +7809,7 @@
         <v>268</v>
       </c>
       <c r="J128" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"114")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H128,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"114")</f>
         <v>114</v>
       </c>
       <c r="K128" s="4"/>
@@ -7861,7 +7858,7 @@
         <v>268</v>
       </c>
       <c r="J129" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"115")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H129,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"115")</f>
         <v>115</v>
       </c>
       <c r="K129" s="4"/>
@@ -7910,7 +7907,7 @@
         <v>268</v>
       </c>
       <c r="J130" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"116")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H130,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"116")</f>
         <v>116</v>
       </c>
       <c r="K130" s="4"/>
@@ -7932,34 +7929,34 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J131" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H131,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"117")</f>
         <v>117</v>
       </c>
       <c r="K131" s="4"/>
@@ -7981,35 +7978,35 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E132" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G132" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H132" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="H132" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J132" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"118")</f>
-        <v>118</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H132,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"117")</f>
+        <v>117</v>
       </c>
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
@@ -8030,19 +8027,19 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D133" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
@@ -8051,13 +8048,13 @@
         <v>351</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J133" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H133,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"118")</f>
         <v>118</v>
       </c>
       <c r="K133" s="4"/>
@@ -8079,35 +8076,35 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D134" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E134" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G134" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H134" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="H134" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J134" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H134,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <v>118</v>
       </c>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
@@ -8128,19 +8125,19 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E135" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
@@ -8149,14 +8146,14 @@
         <v>354</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J135" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H135,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"118")</f>
+        <v>118</v>
       </c>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
@@ -8177,19 +8174,19 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E136" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
@@ -8198,13 +8195,13 @@
         <v>355</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J136" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H136,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"119")</f>
         <v>119</v>
       </c>
       <c r="K136" s="4"/>
@@ -8226,34 +8223,34 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E137" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J137" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H137,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"120")</f>
         <v>120</v>
       </c>
       <c r="K137" s="4"/>
@@ -8275,35 +8272,35 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D138" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E138" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J138" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"121")</f>
-        <v>121</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H138,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
       </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
@@ -8324,19 +8321,19 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D139" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
@@ -8345,14 +8342,14 @@
         <v>360</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>268</v>
       </c>
       <c r="J139" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H139,UNIQUE(FILTER($H$2:$H1068,$H$2:$H1068&lt;&gt;"""")),0),""000"")"),"119")</f>
+        <v>119</v>
       </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
@@ -8372,37 +8369,16 @@
       <c r="Z139" s="4"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="H140" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="I140" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J140" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("TEXT(MATCH(H140,UNIQUE(FILTER($H$2:$H1069,$H$2:$H1069&lt;&gt;"""")),0),""000"")"),"120")</f>
-        <v>120</v>
-      </c>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
@@ -8484,7 +8460,6 @@
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
@@ -8512,6 +8487,7 @@
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
+      <c r="H144" s="6"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
@@ -9260,14 +9236,14 @@
       <c r="Z170" s="4"/>
     </row>
     <row r="171">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="10"/>
+      <c r="G171" s="10"/>
+      <c r="H171" s="10"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -9596,14 +9572,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183">
-      <c r="A183" s="10"/>
-      <c r="B183" s="10"/>
-      <c r="C183" s="10"/>
-      <c r="D183" s="10"/>
-      <c r="E183" s="10"/>
-      <c r="F183" s="10"/>
-      <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -34403,34 +34379,6 @@
       <c r="Y1068" s="4"/>
       <c r="Z1068" s="4"/>
     </row>
-    <row r="1069">
-      <c r="A1069" s="4"/>
-      <c r="B1069" s="4"/>
-      <c r="C1069" s="4"/>
-      <c r="D1069" s="4"/>
-      <c r="E1069" s="4"/>
-      <c r="F1069" s="4"/>
-      <c r="G1069" s="4"/>
-      <c r="H1069" s="4"/>
-      <c r="I1069" s="4"/>
-      <c r="J1069" s="4"/>
-      <c r="K1069" s="4"/>
-      <c r="L1069" s="4"/>
-      <c r="M1069" s="4"/>
-      <c r="N1069" s="4"/>
-      <c r="O1069" s="4"/>
-      <c r="P1069" s="4"/>
-      <c r="Q1069" s="4"/>
-      <c r="R1069" s="4"/>
-      <c r="S1069" s="4"/>
-      <c r="T1069" s="4"/>
-      <c r="U1069" s="4"/>
-      <c r="V1069" s="4"/>
-      <c r="W1069" s="4"/>
-      <c r="X1069" s="4"/>
-      <c r="Y1069" s="4"/>
-      <c r="Z1069" s="4"/>
-    </row>
   </sheetData>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
